--- a/data/proteomics/protein_abundance_across_compartment.xlsx
+++ b/data/proteomics/protein_abundance_across_compartment.xlsx
@@ -535,43 +535,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16714841.87363577</v>
+        <v>16714841.87363578</v>
       </c>
       <c r="D2" t="n">
-        <v>15232930.11836616</v>
+        <v>15232930.11836617</v>
       </c>
       <c r="E2" t="n">
-        <v>16591987.71698642</v>
+        <v>16591987.71698638</v>
       </c>
       <c r="F2" t="n">
         <v>11909762.57876152</v>
       </c>
       <c r="G2" t="n">
-        <v>12430646.91965256</v>
+        <v>12430646.91965255</v>
       </c>
       <c r="H2" t="n">
-        <v>17064878.6242844</v>
+        <v>17064878.62428442</v>
       </c>
       <c r="I2" t="n">
         <v>17318128.62187587</v>
       </c>
       <c r="J2" t="n">
-        <v>14954527.45074675</v>
+        <v>14954527.45074674</v>
       </c>
       <c r="K2" t="n">
-        <v>15106022.61931232</v>
+        <v>15106022.61931233</v>
       </c>
       <c r="L2" t="n">
         <v>14901122.0086805</v>
       </c>
       <c r="M2" t="n">
-        <v>14802785.78604588</v>
+        <v>14802785.78604587</v>
       </c>
       <c r="N2" t="n">
-        <v>15335281.47539596</v>
+        <v>15335281.47539597</v>
       </c>
       <c r="O2" t="n">
-        <v>22481266.00191524</v>
+        <v>22481266.00191523</v>
       </c>
       <c r="P2" t="n">
         <v>22628426.41180001</v>
@@ -580,13 +580,13 @@
         <v>20785172.90428561</v>
       </c>
       <c r="R2" t="n">
-        <v>25992140.79808443</v>
+        <v>25992140.79808441</v>
       </c>
       <c r="S2" t="n">
-        <v>27602721.15237192</v>
+        <v>27602721.15237189</v>
       </c>
       <c r="T2" t="n">
-        <v>27576311.76342786</v>
+        <v>27576311.76342789</v>
       </c>
     </row>
     <row r="3">
@@ -611,7 +611,7 @@
         <v>17241.26746078782</v>
       </c>
       <c r="G3" t="n">
-        <v>18001.62251838347</v>
+        <v>18001.62251838348</v>
       </c>
       <c r="H3" t="n">
         <v>16700.54156221197</v>
@@ -629,13 +629,13 @@
         <v>19787.66344333337</v>
       </c>
       <c r="M3" t="n">
-        <v>19422.72715470945</v>
+        <v>19422.72715470944</v>
       </c>
       <c r="N3" t="n">
         <v>21310.92562847459</v>
       </c>
       <c r="O3" t="n">
-        <v>23271.16053014915</v>
+        <v>23271.16053014914</v>
       </c>
       <c r="P3" t="n">
         <v>24122.98643640589</v>
@@ -681,7 +681,7 @@
         <v>24925.24141843125</v>
       </c>
       <c r="I4" t="n">
-        <v>38071.73339297036</v>
+        <v>38071.73339297035</v>
       </c>
       <c r="J4" t="n">
         <v>32688.15300080674</v>
@@ -690,13 +690,13 @@
         <v>27313.026653393</v>
       </c>
       <c r="L4" t="n">
-        <v>25931.85449007039</v>
+        <v>25931.8544900704</v>
       </c>
       <c r="M4" t="n">
-        <v>36763.60310325294</v>
+        <v>36763.60310325295</v>
       </c>
       <c r="N4" t="n">
-        <v>36961.1918718778</v>
+        <v>36961.19187187782</v>
       </c>
       <c r="O4" t="n">
         <v>44009.61064871498</v>
@@ -705,7 +705,7 @@
         <v>51685.64652877455</v>
       </c>
       <c r="Q4" t="n">
-        <v>49430.7265890936</v>
+        <v>49430.72658909358</v>
       </c>
       <c r="R4" t="n">
         <v>53740.59351281149</v>
@@ -714,7 +714,7 @@
         <v>63559.04387642129</v>
       </c>
       <c r="T4" t="n">
-        <v>65215.71606605414</v>
+        <v>65215.71606605413</v>
       </c>
     </row>
     <row r="5">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1763810.595068699</v>
+        <v>1763810.5950687</v>
       </c>
       <c r="D5" t="n">
         <v>1645626.827158985</v>
@@ -736,7 +736,7 @@
         <v>1483627.043923805</v>
       </c>
       <c r="F5" t="n">
-        <v>1229678.22506825</v>
+        <v>1229678.225068251</v>
       </c>
       <c r="G5" t="n">
         <v>1299961.478084099</v>
@@ -760,7 +760,7 @@
         <v>1279171.708523635</v>
       </c>
       <c r="N5" t="n">
-        <v>1136965.026274923</v>
+        <v>1136965.026274924</v>
       </c>
       <c r="O5" t="n">
         <v>2023692.387487991</v>
@@ -769,16 +769,16 @@
         <v>1989292.29192386</v>
       </c>
       <c r="Q5" t="n">
-        <v>2081248.632774485</v>
+        <v>2081248.632774484</v>
       </c>
       <c r="R5" t="n">
-        <v>2686733.947496927</v>
+        <v>2686733.947496928</v>
       </c>
       <c r="S5" t="n">
-        <v>2985179.080208622</v>
+        <v>2985179.080208621</v>
       </c>
       <c r="T5" t="n">
-        <v>2699354.44758526</v>
+        <v>2699354.447585259</v>
       </c>
     </row>
     <row r="6">
@@ -791,58 +791,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10413004.12493998</v>
+        <v>10413004.12493997</v>
       </c>
       <c r="D6" t="n">
-        <v>9531641.69941452</v>
+        <v>9531641.699414518</v>
       </c>
       <c r="E6" t="n">
-        <v>10746433.95956992</v>
+        <v>10746433.95956991</v>
       </c>
       <c r="F6" t="n">
-        <v>7556281.447736918</v>
+        <v>7556281.447736921</v>
       </c>
       <c r="G6" t="n">
-        <v>7929121.840774878</v>
+        <v>7929121.840774881</v>
       </c>
       <c r="H6" t="n">
-        <v>10780383.16517733</v>
+        <v>10780383.16517732</v>
       </c>
       <c r="I6" t="n">
         <v>10672778.03056934</v>
       </c>
       <c r="J6" t="n">
-        <v>9429950.871609263</v>
+        <v>9429950.871609284</v>
       </c>
       <c r="K6" t="n">
-        <v>9234615.705078559</v>
+        <v>9234615.705078548</v>
       </c>
       <c r="L6" t="n">
-        <v>8821853.429089963</v>
+        <v>8821853.429089967</v>
       </c>
       <c r="M6" t="n">
-        <v>9021699.853657393</v>
+        <v>9021699.853657402</v>
       </c>
       <c r="N6" t="n">
-        <v>9380694.147979498</v>
+        <v>9380694.147979502</v>
       </c>
       <c r="O6" t="n">
-        <v>14003734.02335568</v>
+        <v>14003734.02335569</v>
       </c>
       <c r="P6" t="n">
-        <v>14336033.54296045</v>
+        <v>14336033.54296047</v>
       </c>
       <c r="Q6" t="n">
         <v>13267248.79044553</v>
       </c>
       <c r="R6" t="n">
-        <v>17179774.32837873</v>
+        <v>17179774.32837876</v>
       </c>
       <c r="S6" t="n">
-        <v>18373742.08895308</v>
+        <v>18373742.08895304</v>
       </c>
       <c r="T6" t="n">
-        <v>17678574.56559893</v>
+        <v>17678574.56559895</v>
       </c>
     </row>
     <row r="7">
@@ -855,28 +855,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21830247.55656156</v>
+        <v>21830247.55656157</v>
       </c>
       <c r="D7" t="n">
-        <v>19767170.38213018</v>
+        <v>19767170.38213017</v>
       </c>
       <c r="E7" t="n">
-        <v>20894423.47197612</v>
+        <v>20894423.47197611</v>
       </c>
       <c r="F7" t="n">
-        <v>15630712.08985841</v>
+        <v>15630712.08985843</v>
       </c>
       <c r="G7" t="n">
-        <v>16481115.71307282</v>
+        <v>16481115.71307281</v>
       </c>
       <c r="H7" t="n">
-        <v>23078295.02702035</v>
+        <v>23078295.02702036</v>
       </c>
       <c r="I7" t="n">
         <v>23531551.88454339</v>
       </c>
       <c r="J7" t="n">
-        <v>19978783.18260494</v>
+        <v>19978783.18260489</v>
       </c>
       <c r="K7" t="n">
         <v>20137751.02279409</v>
@@ -891,22 +891,22 @@
         <v>21699854.73952352</v>
       </c>
       <c r="O7" t="n">
-        <v>40071519.55671828</v>
+        <v>40071519.55671829</v>
       </c>
       <c r="P7" t="n">
         <v>39895580.16267175</v>
       </c>
       <c r="Q7" t="n">
-        <v>38002938.13145991</v>
+        <v>38002938.13145989</v>
       </c>
       <c r="R7" t="n">
-        <v>52164131.62160896</v>
+        <v>52164131.62160886</v>
       </c>
       <c r="S7" t="n">
-        <v>54977811.9713097</v>
+        <v>54977811.97130962</v>
       </c>
       <c r="T7" t="n">
-        <v>54268373.92590103</v>
+        <v>54268373.92590108</v>
       </c>
     </row>
     <row r="8">
@@ -919,40 +919,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9374356.637702255</v>
+        <v>9374356.637702243</v>
       </c>
       <c r="D8" t="n">
-        <v>8218581.199281739</v>
+        <v>8218581.199281746</v>
       </c>
       <c r="E8" t="n">
-        <v>8287779.47166939</v>
+        <v>8287779.471669386</v>
       </c>
       <c r="F8" t="n">
-        <v>6655516.599046552</v>
+        <v>6655516.599046554</v>
       </c>
       <c r="G8" t="n">
         <v>6863305.469151915</v>
       </c>
       <c r="H8" t="n">
-        <v>9992598.758686563</v>
+        <v>9992598.758686565</v>
       </c>
       <c r="I8" t="n">
-        <v>9633465.395238137</v>
+        <v>9633465.395238142</v>
       </c>
       <c r="J8" t="n">
-        <v>8511951.881408367</v>
+        <v>8511951.881408364</v>
       </c>
       <c r="K8" t="n">
-        <v>8364450.891004839</v>
+        <v>8364450.891004842</v>
       </c>
       <c r="L8" t="n">
-        <v>7519652.451993989</v>
+        <v>7519652.451993986</v>
       </c>
       <c r="M8" t="n">
         <v>7725303.479826211</v>
       </c>
       <c r="N8" t="n">
-        <v>7829726.753693954</v>
+        <v>7829726.753693953</v>
       </c>
       <c r="O8" t="n">
         <v>12534537.80842077</v>
@@ -964,13 +964,13 @@
         <v>11937254.18574282</v>
       </c>
       <c r="R8" t="n">
-        <v>15650781.56361154</v>
+        <v>15650781.56361155</v>
       </c>
       <c r="S8" t="n">
         <v>17213103.36614148</v>
       </c>
       <c r="T8" t="n">
-        <v>16077401.92873511</v>
+        <v>16077401.9287351</v>
       </c>
     </row>
     <row r="9">
@@ -995,13 +995,13 @@
         <v>1279472.341364926</v>
       </c>
       <c r="G9" t="n">
-        <v>1368121.024972977</v>
+        <v>1368121.024972976</v>
       </c>
       <c r="H9" t="n">
         <v>2059097.637242382</v>
       </c>
       <c r="I9" t="n">
-        <v>1819680.960368376</v>
+        <v>1819680.960368377</v>
       </c>
       <c r="J9" t="n">
         <v>1568171.54403085</v>
@@ -1022,10 +1022,10 @@
         <v>2280060.506511254</v>
       </c>
       <c r="P9" t="n">
-        <v>2198035.684355124</v>
+        <v>2198035.684355125</v>
       </c>
       <c r="Q9" t="n">
-        <v>2404769.066451164</v>
+        <v>2404769.066451165</v>
       </c>
       <c r="R9" t="n">
         <v>3212030.037591445</v>
@@ -1034,7 +1034,7 @@
         <v>3554610.239684647</v>
       </c>
       <c r="T9" t="n">
-        <v>3166736.516147114</v>
+        <v>3166736.516147113</v>
       </c>
     </row>
     <row r="10">
@@ -1050,52 +1050,52 @@
         <v>10372023.86727149</v>
       </c>
       <c r="D10" t="n">
-        <v>9339208.175499372</v>
+        <v>9339208.175499367</v>
       </c>
       <c r="E10" t="n">
-        <v>9110634.194767959</v>
+        <v>9110634.194767954</v>
       </c>
       <c r="F10" t="n">
-        <v>6966216.132993053</v>
+        <v>6966216.132993055</v>
       </c>
       <c r="G10" t="n">
-        <v>7318603.938404121</v>
+        <v>7318603.938404119</v>
       </c>
       <c r="H10" t="n">
         <v>10520657.1884993</v>
       </c>
       <c r="I10" t="n">
-        <v>9795618.438415734</v>
+        <v>9795618.43841573</v>
       </c>
       <c r="J10" t="n">
-        <v>8351998.543747666</v>
+        <v>8351998.543747665</v>
       </c>
       <c r="K10" t="n">
         <v>8523255.164303515</v>
       </c>
       <c r="L10" t="n">
-        <v>8388534.328246878</v>
+        <v>8388534.328246877</v>
       </c>
       <c r="M10" t="n">
-        <v>8165190.129497949</v>
+        <v>8165190.129497947</v>
       </c>
       <c r="N10" t="n">
-        <v>8182535.047625492</v>
+        <v>8182535.047625495</v>
       </c>
       <c r="O10" t="n">
-        <v>13044565.09846656</v>
+        <v>13044565.09846655</v>
       </c>
       <c r="P10" t="n">
-        <v>13166788.26792787</v>
+        <v>13166788.26792786</v>
       </c>
       <c r="Q10" t="n">
-        <v>13002883.83567924</v>
+        <v>13002883.83567923</v>
       </c>
       <c r="R10" t="n">
-        <v>16498891.24259684</v>
+        <v>16498891.24259685</v>
       </c>
       <c r="S10" t="n">
-        <v>17926365.86044455</v>
+        <v>17926365.86044454</v>
       </c>
       <c r="T10" t="n">
         <v>17157878.75153312</v>
@@ -1117,7 +1117,7 @@
         <v>2978751.833096653</v>
       </c>
       <c r="E11" t="n">
-        <v>2582483.332878907</v>
+        <v>2582483.332878908</v>
       </c>
       <c r="F11" t="n">
         <v>2094145.437336253</v>
@@ -1126,7 +1126,7 @@
         <v>2125951.014830024</v>
       </c>
       <c r="H11" t="n">
-        <v>4161830.157214137</v>
+        <v>4161830.157214138</v>
       </c>
       <c r="I11" t="n">
         <v>3373024.939158957</v>
@@ -1147,22 +1147,22 @@
         <v>2196945.902520687</v>
       </c>
       <c r="O11" t="n">
-        <v>4262056.603513389</v>
+        <v>4262056.603513388</v>
       </c>
       <c r="P11" t="n">
         <v>4325140.218909103</v>
       </c>
       <c r="Q11" t="n">
-        <v>4273434.782215408</v>
+        <v>4273434.78221541</v>
       </c>
       <c r="R11" t="n">
-        <v>5733772.593878118</v>
+        <v>5733772.593878116</v>
       </c>
       <c r="S11" t="n">
         <v>7179688.989360151</v>
       </c>
       <c r="T11" t="n">
-        <v>6026663.26653611</v>
+        <v>6026663.266536111</v>
       </c>
     </row>
     <row r="12">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1168663.311594959</v>
+        <v>1168663.31159496</v>
       </c>
       <c r="D12" t="n">
-        <v>1060374.531166172</v>
+        <v>1060374.531166171</v>
       </c>
       <c r="E12" t="n">
         <v>1025014.323031393</v>
       </c>
       <c r="F12" t="n">
-        <v>870197.4397913039</v>
+        <v>870197.439791303</v>
       </c>
       <c r="G12" t="n">
-        <v>957218.4782320736</v>
+        <v>957218.4782320739</v>
       </c>
       <c r="H12" t="n">
-        <v>920435.8324875686</v>
+        <v>920435.8324875684</v>
       </c>
       <c r="I12" t="n">
-        <v>1345983.388776784</v>
+        <v>1345983.388776785</v>
       </c>
       <c r="J12" t="n">
-        <v>1128229.798266864</v>
+        <v>1128229.798266863</v>
       </c>
       <c r="K12" t="n">
         <v>1216571.478407286</v>
@@ -1205,13 +1205,13 @@
         <v>1275921.296576543</v>
       </c>
       <c r="M12" t="n">
-        <v>1182356.50050618</v>
+        <v>1182356.500506181</v>
       </c>
       <c r="N12" t="n">
-        <v>1266236.532628594</v>
+        <v>1266236.532628595</v>
       </c>
       <c r="O12" t="n">
-        <v>1675927.537795617</v>
+        <v>1675927.537795616</v>
       </c>
       <c r="P12" t="n">
         <v>1715476.849481077</v>
@@ -1226,7 +1226,7 @@
         <v>2048972.213074397</v>
       </c>
       <c r="T12" t="n">
-        <v>2123969.866962702</v>
+        <v>2123969.866962703</v>
       </c>
     </row>
     <row r="13">
@@ -1254,10 +1254,10 @@
         <v>124299.0373156967</v>
       </c>
       <c r="H13" t="n">
-        <v>100628.0469396678</v>
+        <v>100628.0469396677</v>
       </c>
       <c r="I13" t="n">
-        <v>183755.693917004</v>
+        <v>183755.6939170039</v>
       </c>
       <c r="J13" t="n">
         <v>147714.7399585223</v>
@@ -1275,7 +1275,7 @@
         <v>176313.2365273632</v>
       </c>
       <c r="O13" t="n">
-        <v>215292.0633574529</v>
+        <v>215292.063357453</v>
       </c>
       <c r="P13" t="n">
         <v>195917.6980750659</v>
@@ -1284,10 +1284,10 @@
         <v>218479.5135039496</v>
       </c>
       <c r="R13" t="n">
-        <v>184746.4055835291</v>
+        <v>184746.4055835292</v>
       </c>
       <c r="S13" t="n">
-        <v>220129.8953455987</v>
+        <v>220129.8953455988</v>
       </c>
       <c r="T13" t="n">
         <v>226813.2241753651</v>
@@ -1303,46 +1303,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>834715.8456368501</v>
+        <v>834715.8456368502</v>
       </c>
       <c r="D14" t="n">
-        <v>823171.0153827948</v>
+        <v>823171.0153827952</v>
       </c>
       <c r="E14" t="n">
-        <v>949692.1590519331</v>
+        <v>949692.1590519329</v>
       </c>
       <c r="F14" t="n">
-        <v>567937.0478878963</v>
+        <v>567937.047887896</v>
       </c>
       <c r="G14" t="n">
         <v>657690.7136289364</v>
       </c>
       <c r="H14" t="n">
-        <v>844413.5163058153</v>
+        <v>844413.5163058154</v>
       </c>
       <c r="I14" t="n">
-        <v>940184.107105138</v>
+        <v>940184.1071051382</v>
       </c>
       <c r="J14" t="n">
-        <v>798168.4194148075</v>
+        <v>798168.4194148073</v>
       </c>
       <c r="K14" t="n">
-        <v>774331.1068249195</v>
+        <v>774331.1068249196</v>
       </c>
       <c r="L14" t="n">
-        <v>782729.7436533226</v>
+        <v>782729.7436533223</v>
       </c>
       <c r="M14" t="n">
-        <v>738854.3707156571</v>
+        <v>738854.370715657</v>
       </c>
       <c r="N14" t="n">
-        <v>811174.5595378791</v>
+        <v>811174.5595378793</v>
       </c>
       <c r="O14" t="n">
-        <v>940458.3342795809</v>
+        <v>940458.3342795807</v>
       </c>
       <c r="P14" t="n">
-        <v>967774.7543784805</v>
+        <v>967774.7543784804</v>
       </c>
       <c r="Q14" t="n">
         <v>843111.4744124073</v>
@@ -1382,19 +1382,19 @@
         <v>117878.2340485532</v>
       </c>
       <c r="H15" t="n">
-        <v>237945.0927120042</v>
+        <v>237945.0927120041</v>
       </c>
       <c r="I15" t="n">
         <v>242612.6349684847</v>
       </c>
       <c r="J15" t="n">
-        <v>206752.7645258473</v>
+        <v>206752.7645258472</v>
       </c>
       <c r="K15" t="n">
-        <v>188495.2314503218</v>
+        <v>188495.2314503219</v>
       </c>
       <c r="L15" t="n">
-        <v>183413.1511820448</v>
+        <v>183413.1511820449</v>
       </c>
       <c r="M15" t="n">
         <v>167213.8935593245</v>
@@ -1409,7 +1409,7 @@
         <v>278205.4186235255</v>
       </c>
       <c r="Q15" t="n">
-        <v>218085.8615098751</v>
+        <v>218085.8615098752</v>
       </c>
       <c r="R15" t="n">
         <v>269778.1954708219</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>198652.4200168981</v>
+        <v>198652.420016898</v>
       </c>
       <c r="D16" t="n">
         <v>196871.0913880663</v>
@@ -1440,7 +1440,7 @@
         <v>183846.3916360076</v>
       </c>
       <c r="F16" t="n">
-        <v>176522.8065629424</v>
+        <v>176522.8065629423</v>
       </c>
       <c r="G16" t="n">
         <v>179147.5193105745</v>
@@ -1452,10 +1452,10 @@
         <v>234940.3187871656</v>
       </c>
       <c r="J16" t="n">
-        <v>181794.9223792295</v>
+        <v>181794.9223792296</v>
       </c>
       <c r="K16" t="n">
-        <v>210937.729473092</v>
+        <v>210937.7294730921</v>
       </c>
       <c r="L16" t="n">
         <v>220535.6007597612</v>
@@ -1507,10 +1507,10 @@
         <v>253502.9567492802</v>
       </c>
       <c r="G17" t="n">
-        <v>292385.9926381908</v>
+        <v>292385.9926381909</v>
       </c>
       <c r="H17" t="n">
-        <v>302873.3048633508</v>
+        <v>302873.3048633505</v>
       </c>
       <c r="I17" t="n">
         <v>480238.5988031732</v>
@@ -1519,31 +1519,31 @@
         <v>399539.2122226661</v>
       </c>
       <c r="K17" t="n">
-        <v>220168.5544916144</v>
+        <v>220168.5544916143</v>
       </c>
       <c r="L17" t="n">
-        <v>433448.9450338317</v>
+        <v>433448.9450338318</v>
       </c>
       <c r="M17" t="n">
         <v>397111.9015895578</v>
       </c>
       <c r="N17" t="n">
-        <v>419612.8187865195</v>
+        <v>419612.8187865193</v>
       </c>
       <c r="O17" t="n">
-        <v>205578.137336372</v>
+        <v>205578.1373363719</v>
       </c>
       <c r="P17" t="n">
-        <v>562971.3223546974</v>
+        <v>562971.3223546972</v>
       </c>
       <c r="Q17" t="n">
-        <v>486137.6153136077</v>
+        <v>486137.6153136076</v>
       </c>
       <c r="R17" t="n">
-        <v>556395.2502073111</v>
+        <v>556395.250207311</v>
       </c>
       <c r="S17" t="n">
-        <v>578804.2987210541</v>
+        <v>578804.2987210543</v>
       </c>
       <c r="T17" t="n">
         <v>580188.9430927075</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>312968.9184962493</v>
+        <v>312968.9184962494</v>
       </c>
       <c r="D18" t="n">
         <v>274154.8440673107</v>
@@ -1568,10 +1568,10 @@
         <v>256142.2798375115</v>
       </c>
       <c r="F18" t="n">
-        <v>220698.6113636954</v>
+        <v>220698.6113636956</v>
       </c>
       <c r="G18" t="n">
-        <v>244675.9344991827</v>
+        <v>244675.9344991826</v>
       </c>
       <c r="H18" t="n">
         <v>215349.2330518003</v>
@@ -1580,16 +1580,16 @@
         <v>346533.9829200538</v>
       </c>
       <c r="J18" t="n">
-        <v>275681.3891445102</v>
+        <v>275681.3891445103</v>
       </c>
       <c r="K18" t="n">
-        <v>325670.6751403048</v>
+        <v>325670.6751403047</v>
       </c>
       <c r="L18" t="n">
         <v>328077.5348369596</v>
       </c>
       <c r="M18" t="n">
-        <v>313302.1250224906</v>
+        <v>313302.1250224907</v>
       </c>
       <c r="N18" t="n">
         <v>320596.311319011</v>
@@ -1598,7 +1598,7 @@
         <v>457595.2422215434</v>
       </c>
       <c r="P18" t="n">
-        <v>462132.924961494</v>
+        <v>462132.9249614939</v>
       </c>
       <c r="Q18" t="n">
         <v>424515.0100769097</v>
@@ -1607,10 +1607,10 @@
         <v>530706.7728003307</v>
       </c>
       <c r="S18" t="n">
-        <v>654651.5965562728</v>
+        <v>654651.5965562725</v>
       </c>
       <c r="T18" t="n">
-        <v>679166.4772766577</v>
+        <v>679166.4772766581</v>
       </c>
     </row>
     <row r="19">
@@ -1626,40 +1626,40 @@
         <v>102123.873443456</v>
       </c>
       <c r="D19" t="n">
-        <v>90764.91601610632</v>
+        <v>90764.91601610635</v>
       </c>
       <c r="E19" t="n">
-        <v>92223.43925599942</v>
+        <v>92223.43925599943</v>
       </c>
       <c r="F19" t="n">
-        <v>79006.83366850892</v>
+        <v>79006.83366850893</v>
       </c>
       <c r="G19" t="n">
-        <v>82340.00557320329</v>
+        <v>82340.00557320328</v>
       </c>
       <c r="H19" t="n">
         <v>100183.8343918151</v>
       </c>
       <c r="I19" t="n">
-        <v>128894.7581009818</v>
+        <v>128894.7581009819</v>
       </c>
       <c r="J19" t="n">
         <v>112161.2221695338</v>
       </c>
       <c r="K19" t="n">
-        <v>111000.6935050629</v>
+        <v>111000.6935050628</v>
       </c>
       <c r="L19" t="n">
-        <v>116527.852946617</v>
+        <v>116527.8529466169</v>
       </c>
       <c r="M19" t="n">
-        <v>112692.7415326637</v>
+        <v>112692.7415326636</v>
       </c>
       <c r="N19" t="n">
-        <v>111840.8453097917</v>
+        <v>111840.8453097918</v>
       </c>
       <c r="O19" t="n">
-        <v>163186.1075008595</v>
+        <v>163186.1075008594</v>
       </c>
       <c r="P19" t="n">
         <v>163218.6857479754</v>
@@ -1671,10 +1671,10 @@
         <v>204358.6433835821</v>
       </c>
       <c r="S19" t="n">
-        <v>219693.1177947776</v>
+        <v>219693.1177947777</v>
       </c>
       <c r="T19" t="n">
-        <v>209326.9121779554</v>
+        <v>209326.9121779553</v>
       </c>
     </row>
     <row r="20">
@@ -1687,55 +1687,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>314069.399305274</v>
+        <v>314069.3993052738</v>
       </c>
       <c r="D20" t="n">
-        <v>271770.2475060593</v>
+        <v>271770.2475060591</v>
       </c>
       <c r="E20" t="n">
-        <v>301767.0379106121</v>
+        <v>301767.037910612</v>
       </c>
       <c r="F20" t="n">
         <v>255800.3941776927</v>
       </c>
       <c r="G20" t="n">
-        <v>276719.6982961026</v>
+        <v>276719.6982961028</v>
       </c>
       <c r="H20" t="n">
-        <v>350412.0275945536</v>
+        <v>350412.0275945537</v>
       </c>
       <c r="I20" t="n">
-        <v>397163.6351116429</v>
+        <v>397163.6351116428</v>
       </c>
       <c r="J20" t="n">
-        <v>342207.6963823137</v>
+        <v>342207.6963823139</v>
       </c>
       <c r="K20" t="n">
         <v>347253.2073858863</v>
       </c>
       <c r="L20" t="n">
-        <v>396597.3078990277</v>
+        <v>396597.3078990275</v>
       </c>
       <c r="M20" t="n">
-        <v>398800.8082719819</v>
+        <v>398800.808271982</v>
       </c>
       <c r="N20" t="n">
-        <v>353957.9227834843</v>
+        <v>353957.9227834842</v>
       </c>
       <c r="O20" t="n">
-        <v>660739.9476472138</v>
+        <v>660739.9476472139</v>
       </c>
       <c r="P20" t="n">
-        <v>643230.1158241876</v>
+        <v>643230.1158241878</v>
       </c>
       <c r="Q20" t="n">
-        <v>614423.7874753544</v>
+        <v>614423.7874753543</v>
       </c>
       <c r="R20" t="n">
-        <v>764844.2173257929</v>
+        <v>764844.2173257931</v>
       </c>
       <c r="S20" t="n">
-        <v>714912.9924305234</v>
+        <v>714912.9924305235</v>
       </c>
       <c r="T20" t="n">
         <v>810462.8444204209</v>
@@ -1824,7 +1824,7 @@
         <v>29810.47927727097</v>
       </c>
       <c r="F22" t="n">
-        <v>22710.54238569897</v>
+        <v>22710.54238569898</v>
       </c>
       <c r="G22" t="n">
         <v>25097.79541800509</v>
@@ -1833,22 +1833,22 @@
         <v>26406.38282961162</v>
       </c>
       <c r="I22" t="n">
-        <v>37113.52979592493</v>
+        <v>37113.52979592494</v>
       </c>
       <c r="J22" t="n">
-        <v>32748.55487985369</v>
+        <v>32748.55487985368</v>
       </c>
       <c r="K22" t="n">
         <v>33140.71007698659</v>
       </c>
       <c r="L22" t="n">
-        <v>34555.79748095958</v>
+        <v>34555.79748095957</v>
       </c>
       <c r="M22" t="n">
         <v>33957.64410196402</v>
       </c>
       <c r="N22" t="n">
-        <v>36888.11711507788</v>
+        <v>36888.11711507787</v>
       </c>
       <c r="O22" t="n">
         <v>49478.30407758765</v>
@@ -1857,16 +1857,16 @@
         <v>52555.50705579756</v>
       </c>
       <c r="Q22" t="n">
-        <v>45891.23776677194</v>
+        <v>45891.23776677196</v>
       </c>
       <c r="R22" t="n">
-        <v>58174.43420578599</v>
+        <v>58174.434205786</v>
       </c>
       <c r="S22" t="n">
         <v>60322.62501235925</v>
       </c>
       <c r="T22" t="n">
-        <v>61521.46123353795</v>
+        <v>61521.46123353796</v>
       </c>
     </row>
     <row r="23">
@@ -1891,7 +1891,7 @@
         <v>1138298.360824973</v>
       </c>
       <c r="G23" t="n">
-        <v>1076960.77043313</v>
+        <v>1076960.770433131</v>
       </c>
       <c r="H23" t="n">
         <v>2958027.92862541</v>
@@ -1903,13 +1903,13 @@
         <v>1841483.255656051</v>
       </c>
       <c r="K23" t="n">
-        <v>1700696.58335369</v>
+        <v>1700696.583353689</v>
       </c>
       <c r="L23" t="n">
-        <v>1410968.547508169</v>
+        <v>1410968.547508168</v>
       </c>
       <c r="M23" t="n">
-        <v>1571164.639854621</v>
+        <v>1571164.63985462</v>
       </c>
       <c r="N23" t="n">
         <v>1422858.960910451</v>
@@ -1918,10 +1918,10 @@
         <v>2576561.648811951</v>
       </c>
       <c r="P23" t="n">
-        <v>2667780.81410815</v>
+        <v>2667780.814108151</v>
       </c>
       <c r="Q23" t="n">
-        <v>2507436.880300541</v>
+        <v>2507436.88030054</v>
       </c>
       <c r="R23" t="n">
         <v>3338011.976540202</v>
@@ -1930,7 +1930,7 @@
         <v>4376106.841540868</v>
       </c>
       <c r="T23" t="n">
-        <v>3600613.133302301</v>
+        <v>3600613.133302302</v>
       </c>
     </row>
     <row r="24">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8141.749540143105</v>
+        <v>8141.749540143104</v>
       </c>
       <c r="D24" t="n">
         <v>8382.151350533941</v>
@@ -1952,7 +1952,7 @@
         <v>9212.1462282714</v>
       </c>
       <c r="F24" t="n">
-        <v>7875.391235204565</v>
+        <v>7875.391235204564</v>
       </c>
       <c r="G24" t="n">
         <v>7499.319045288297</v>
@@ -1988,7 +1988,7 @@
         <v>18051.78975688652</v>
       </c>
       <c r="R24" t="n">
-        <v>18011.28948185952</v>
+        <v>18011.28948185953</v>
       </c>
       <c r="S24" t="n">
         <v>21092.65736245934</v>
@@ -2013,13 +2013,13 @@
         <v>110201.2237942159</v>
       </c>
       <c r="E25" t="n">
-        <v>115028.6844655728</v>
+        <v>115028.6844655729</v>
       </c>
       <c r="F25" t="n">
-        <v>89067.87842878707</v>
+        <v>89067.87842878709</v>
       </c>
       <c r="G25" t="n">
-        <v>98721.14868078684</v>
+        <v>98721.14868078681</v>
       </c>
       <c r="H25" t="n">
         <v>152780.2207994705</v>
@@ -2037,13 +2037,13 @@
         <v>127931.0548566602</v>
       </c>
       <c r="M25" t="n">
-        <v>124242.6322242842</v>
+        <v>124242.6322242841</v>
       </c>
       <c r="N25" t="n">
         <v>127864.7031438811</v>
       </c>
       <c r="O25" t="n">
-        <v>184777.7506208747</v>
+        <v>184777.7506208748</v>
       </c>
       <c r="P25" t="n">
         <v>188201.1189160087</v>
@@ -2052,13 +2052,13 @@
         <v>167920.078545073</v>
       </c>
       <c r="R25" t="n">
-        <v>194629.3102681093</v>
+        <v>194629.3102681092</v>
       </c>
       <c r="S25" t="n">
         <v>200374.027975655</v>
       </c>
       <c r="T25" t="n">
-        <v>218596.8625652174</v>
+        <v>218596.8625652173</v>
       </c>
     </row>
     <row r="26">
@@ -2074,7 +2074,7 @@
         <v>163803.2615188189</v>
       </c>
       <c r="D26" t="n">
-        <v>153285.7204774482</v>
+        <v>153285.7204774481</v>
       </c>
       <c r="E26" t="n">
         <v>141321.9087183225</v>
@@ -2101,19 +2101,19 @@
         <v>200728.4706114925</v>
       </c>
       <c r="M26" t="n">
-        <v>184444.8400201081</v>
+        <v>184444.840020108</v>
       </c>
       <c r="N26" t="n">
-        <v>193237.7039160114</v>
+        <v>193237.7039160113</v>
       </c>
       <c r="O26" t="n">
-        <v>233808.2964108737</v>
+        <v>233808.2964108736</v>
       </c>
       <c r="P26" t="n">
-        <v>222828.6174822639</v>
+        <v>222828.6174822638</v>
       </c>
       <c r="Q26" t="n">
-        <v>213814.5592531317</v>
+        <v>213814.5592531316</v>
       </c>
       <c r="R26" t="n">
         <v>243808.9905859077</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1202940.566162279</v>
+        <v>1202940.56616228</v>
       </c>
       <c r="D27" t="n">
         <v>1028672.412187272</v>
@@ -2144,13 +2144,13 @@
         <v>1138815.656105632</v>
       </c>
       <c r="F27" t="n">
-        <v>987758.0807930317</v>
+        <v>987758.0807930315</v>
       </c>
       <c r="G27" t="n">
-        <v>974934.3454348554</v>
+        <v>974934.3454348557</v>
       </c>
       <c r="H27" t="n">
-        <v>1363450.480167271</v>
+        <v>1363450.480167272</v>
       </c>
       <c r="I27" t="n">
         <v>1527425.736349651</v>
@@ -2159,10 +2159,10 @@
         <v>1280417.59218315</v>
       </c>
       <c r="K27" t="n">
-        <v>1246655.150470378</v>
+        <v>1246655.150470377</v>
       </c>
       <c r="L27" t="n">
-        <v>1623281.913506034</v>
+        <v>1623281.913506035</v>
       </c>
       <c r="M27" t="n">
         <v>1551518.628723045</v>
@@ -2174,19 +2174,19 @@
         <v>3179964.813637731</v>
       </c>
       <c r="P27" t="n">
-        <v>3411522.121280713</v>
+        <v>3411522.121280712</v>
       </c>
       <c r="Q27" t="n">
-        <v>3168525.720279138</v>
+        <v>3168525.72027914</v>
       </c>
       <c r="R27" t="n">
-        <v>4637475.98350445</v>
+        <v>4637475.983504454</v>
       </c>
       <c r="S27" t="n">
         <v>5094744.507293523</v>
       </c>
       <c r="T27" t="n">
-        <v>4926253.43265368</v>
+        <v>4926253.432653682</v>
       </c>
     </row>
     <row r="28">
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25298.74945347713</v>
+        <v>25298.74945347714</v>
       </c>
       <c r="D28" t="n">
         <v>22844.15002109188</v>
       </c>
       <c r="E28" t="n">
-        <v>28056.02681827395</v>
+        <v>28056.02681827396</v>
       </c>
       <c r="F28" t="n">
         <v>21722.2816818514</v>
       </c>
       <c r="G28" t="n">
-        <v>21879.12321400491</v>
+        <v>21879.12321400492</v>
       </c>
       <c r="H28" t="n">
         <v>23982.9150941009</v>
@@ -2226,13 +2226,13 @@
         <v>25179.35027134308</v>
       </c>
       <c r="L28" t="n">
-        <v>26532.28291903977</v>
+        <v>26532.28291903976</v>
       </c>
       <c r="M28" t="n">
-        <v>27084.11373783786</v>
+        <v>27084.11373783787</v>
       </c>
       <c r="N28" t="n">
-        <v>26055.42478092446</v>
+        <v>26055.42478092447</v>
       </c>
       <c r="O28" t="n">
         <v>39302.58988156103</v>
@@ -2250,7 +2250,7 @@
         <v>41039.59011664874</v>
       </c>
       <c r="T28" t="n">
-        <v>43041.72569769447</v>
+        <v>43041.72569769448</v>
       </c>
     </row>
     <row r="29">
@@ -2269,28 +2269,28 @@
         <v>1356051.78024754</v>
       </c>
       <c r="E29" t="n">
-        <v>1433080.088807169</v>
+        <v>1433080.088807168</v>
       </c>
       <c r="F29" t="n">
         <v>1005718.083170145</v>
       </c>
       <c r="G29" t="n">
-        <v>1173051.060575702</v>
+        <v>1173051.060575703</v>
       </c>
       <c r="H29" t="n">
-        <v>967233.2264007597</v>
+        <v>967233.2264007598</v>
       </c>
       <c r="I29" t="n">
-        <v>1325088.038671965</v>
+        <v>1325088.038671964</v>
       </c>
       <c r="J29" t="n">
         <v>1111051.08577994</v>
       </c>
       <c r="K29" t="n">
-        <v>1226978.522643897</v>
+        <v>1226978.522643898</v>
       </c>
       <c r="L29" t="n">
-        <v>1250703.591719183</v>
+        <v>1250703.591719182</v>
       </c>
       <c r="M29" t="n">
         <v>1173750.758252523</v>
@@ -2299,19 +2299,19 @@
         <v>1278438.316606552</v>
       </c>
       <c r="O29" t="n">
-        <v>1519323.683533903</v>
+        <v>1519323.683533904</v>
       </c>
       <c r="P29" t="n">
-        <v>1549598.949884841</v>
+        <v>1549598.949884842</v>
       </c>
       <c r="Q29" t="n">
-        <v>1463447.193932263</v>
+        <v>1463447.193932264</v>
       </c>
       <c r="R29" t="n">
         <v>1587848.078454697</v>
       </c>
       <c r="S29" t="n">
-        <v>1672505.455743814</v>
+        <v>1672505.455743813</v>
       </c>
       <c r="T29" t="n">
         <v>1835700.306702235</v>
@@ -2366,7 +2366,7 @@
         <v>2936.073840698726</v>
       </c>
       <c r="P30" t="n">
-        <v>3150.4539101999</v>
+        <v>3150.453910199899</v>
       </c>
       <c r="Q30" t="n">
         <v>2786.718592677217</v>
@@ -2375,7 +2375,7 @@
         <v>3786.385190680816</v>
       </c>
       <c r="S30" t="n">
-        <v>2613.434163612546</v>
+        <v>2613.434163612547</v>
       </c>
       <c r="T30" t="n">
         <v>2850.973204826895</v>
@@ -2394,7 +2394,7 @@
         <v>267.4349060559088</v>
       </c>
       <c r="D31" t="n">
-        <v>269.2346135931035</v>
+        <v>269.2346135931034</v>
       </c>
       <c r="E31" t="n">
         <v>308.4478866047898</v>
@@ -2461,7 +2461,7 @@
         <v>1786168.182025759</v>
       </c>
       <c r="E32" t="n">
-        <v>2487511.863270836</v>
+        <v>2487511.863270835</v>
       </c>
       <c r="F32" t="n">
         <v>1329776.784110882</v>
@@ -2470,16 +2470,16 @@
         <v>1405643.416677078</v>
       </c>
       <c r="H32" t="n">
-        <v>2143575.795746203</v>
+        <v>2143575.795746204</v>
       </c>
       <c r="I32" t="n">
-        <v>1856678.6917103</v>
+        <v>1856678.691710299</v>
       </c>
       <c r="J32" t="n">
         <v>1587944.053287883</v>
       </c>
       <c r="K32" t="n">
-        <v>1657680.686880097</v>
+        <v>1657680.686880096</v>
       </c>
       <c r="L32" t="n">
         <v>1807846.37301377</v>
@@ -2491,13 +2491,13 @@
         <v>1695729.870273703</v>
       </c>
       <c r="O32" t="n">
-        <v>3067214.291342129</v>
+        <v>3067214.29134213</v>
       </c>
       <c r="P32" t="n">
-        <v>2868918.428123059</v>
+        <v>2868918.42812306</v>
       </c>
       <c r="Q32" t="n">
-        <v>2826410.369330301</v>
+        <v>2826410.3693303</v>
       </c>
       <c r="R32" t="n">
         <v>4084600.622010314</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2767253.342534125</v>
+        <v>2767253.342534124</v>
       </c>
       <c r="D33" t="n">
         <v>2455718.988921544</v>
@@ -2531,7 +2531,7 @@
         <v>2419204.927143553</v>
       </c>
       <c r="G33" t="n">
-        <v>2509487.593609374</v>
+        <v>2509487.593609375</v>
       </c>
       <c r="H33" t="n">
         <v>2955242.334596582</v>
@@ -2543,10 +2543,10 @@
         <v>2978953.665070162</v>
       </c>
       <c r="K33" t="n">
-        <v>2770033.435830506</v>
+        <v>2770033.435830505</v>
       </c>
       <c r="L33" t="n">
-        <v>2346544.198923407</v>
+        <v>2346544.198923408</v>
       </c>
       <c r="M33" t="n">
         <v>2457467.238241151</v>
@@ -2564,13 +2564,13 @@
         <v>3307672.798898404</v>
       </c>
       <c r="R33" t="n">
-        <v>3775326.657476424</v>
+        <v>3775326.657476423</v>
       </c>
       <c r="S33" t="n">
         <v>3755324.854652141</v>
       </c>
       <c r="T33" t="n">
-        <v>3885110.330815147</v>
+        <v>3885110.330815148</v>
       </c>
     </row>
     <row r="34">
@@ -2589,19 +2589,19 @@
         <v>45911.35876084832</v>
       </c>
       <c r="E34" t="n">
-        <v>45774.34806417147</v>
+        <v>45774.34806417148</v>
       </c>
       <c r="F34" t="n">
-        <v>36965.10531074317</v>
+        <v>36965.10531074318</v>
       </c>
       <c r="G34" t="n">
-        <v>38382.16218719399</v>
+        <v>38382.16218719398</v>
       </c>
       <c r="H34" t="n">
-        <v>53115.99890504132</v>
+        <v>53115.99890504131</v>
       </c>
       <c r="I34" t="n">
-        <v>70872.14098761011</v>
+        <v>70872.14098761012</v>
       </c>
       <c r="J34" t="n">
         <v>60729.13546639599</v>
@@ -2610,10 +2610,10 @@
         <v>59254.00885179613</v>
       </c>
       <c r="L34" t="n">
-        <v>61881.49107022695</v>
+        <v>61881.49107022694</v>
       </c>
       <c r="M34" t="n">
-        <v>58631.28221576838</v>
+        <v>58631.2822157684</v>
       </c>
       <c r="N34" t="n">
         <v>54782.16518187412</v>
@@ -2622,10 +2622,10 @@
         <v>92975.72038508201</v>
       </c>
       <c r="P34" t="n">
-        <v>87793.07477370645</v>
+        <v>87793.07477370642</v>
       </c>
       <c r="Q34" t="n">
-        <v>75888.27068824579</v>
+        <v>75888.2706882458</v>
       </c>
       <c r="R34" t="n">
         <v>125891.9500524409</v>
@@ -2647,43 +2647,43 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>52585.02099398034</v>
+        <v>52585.02099398033</v>
       </c>
       <c r="D35" t="n">
         <v>48794.65508405893</v>
       </c>
       <c r="E35" t="n">
-        <v>45713.63676660268</v>
+        <v>45713.63676660267</v>
       </c>
       <c r="F35" t="n">
-        <v>39381.44849531932</v>
+        <v>39381.44849531933</v>
       </c>
       <c r="G35" t="n">
-        <v>39693.15499451639</v>
+        <v>39693.15499451638</v>
       </c>
       <c r="H35" t="n">
         <v>61082.38160215941</v>
       </c>
       <c r="I35" t="n">
-        <v>71050.2001920209</v>
+        <v>71050.20019202091</v>
       </c>
       <c r="J35" t="n">
         <v>56814.1260985986</v>
       </c>
       <c r="K35" t="n">
-        <v>59578.54897739022</v>
+        <v>59578.54897739023</v>
       </c>
       <c r="L35" t="n">
         <v>61142.27978475414</v>
       </c>
       <c r="M35" t="n">
-        <v>57635.69080103684</v>
+        <v>57635.69080103686</v>
       </c>
       <c r="N35" t="n">
         <v>56207.69768464223</v>
       </c>
       <c r="O35" t="n">
-        <v>95868.40074296352</v>
+        <v>95868.40074296354</v>
       </c>
       <c r="P35" t="n">
         <v>95323.69379041529</v>
@@ -2692,7 +2692,7 @@
         <v>88684.70915774038</v>
       </c>
       <c r="R35" t="n">
-        <v>94814.795177059</v>
+        <v>94814.79517705899</v>
       </c>
       <c r="S35" t="n">
         <v>112323.1102878436</v>
@@ -2720,10 +2720,10 @@
         <v>110758.3728007447</v>
       </c>
       <c r="F36" t="n">
-        <v>94539.85004338966</v>
+        <v>94539.85004338967</v>
       </c>
       <c r="G36" t="n">
-        <v>95533.40289710107</v>
+        <v>95533.40289710106</v>
       </c>
       <c r="H36" t="n">
         <v>79931.97377673081</v>
@@ -2732,7 +2732,7 @@
         <v>136511.7520499656</v>
       </c>
       <c r="J36" t="n">
-        <v>118002.8175826912</v>
+        <v>118002.8175826913</v>
       </c>
       <c r="K36" t="n">
         <v>119048.3022167206</v>
@@ -2750,7 +2750,7 @@
         <v>174419.6964964904</v>
       </c>
       <c r="P36" t="n">
-        <v>190156.1270534142</v>
+        <v>190156.1270534143</v>
       </c>
       <c r="Q36" t="n">
         <v>186591.6246404683</v>
@@ -2778,22 +2778,22 @@
         <v>536885.8673563829</v>
       </c>
       <c r="D37" t="n">
-        <v>442687.8914548552</v>
+        <v>442687.8914548551</v>
       </c>
       <c r="E37" t="n">
-        <v>509074.8116835099</v>
+        <v>509074.81168351</v>
       </c>
       <c r="F37" t="n">
         <v>379588.5718271977</v>
       </c>
       <c r="G37" t="n">
-        <v>407960.5676490155</v>
+        <v>407960.5676490156</v>
       </c>
       <c r="H37" t="n">
-        <v>600801.5156699935</v>
+        <v>600801.5156699937</v>
       </c>
       <c r="I37" t="n">
-        <v>651958.2159596542</v>
+        <v>651958.2159596541</v>
       </c>
       <c r="J37" t="n">
         <v>571665.8580236606</v>
@@ -2802,7 +2802,7 @@
         <v>590064.5848326255</v>
       </c>
       <c r="L37" t="n">
-        <v>614529.1835452917</v>
+        <v>614529.1835452915</v>
       </c>
       <c r="M37" t="n">
         <v>590172.0415807007</v>
@@ -2814,19 +2814,19 @@
         <v>775508.7374797686</v>
       </c>
       <c r="P37" t="n">
-        <v>802665.3789687783</v>
+        <v>802665.3789687781</v>
       </c>
       <c r="Q37" t="n">
-        <v>727757.6502118049</v>
+        <v>727757.650211805</v>
       </c>
       <c r="R37" t="n">
-        <v>830449.6473378068</v>
+        <v>830449.6473378066</v>
       </c>
       <c r="S37" t="n">
-        <v>764493.4075781762</v>
+        <v>764493.4075781764</v>
       </c>
       <c r="T37" t="n">
-        <v>900391.4640649841</v>
+        <v>900391.4640649843</v>
       </c>
     </row>
     <row r="38">
@@ -2842,7 +2842,7 @@
         <v>19338.21816621962</v>
       </c>
       <c r="D38" t="n">
-        <v>18340.71459701418</v>
+        <v>18340.71459701417</v>
       </c>
       <c r="E38" t="n">
         <v>19745.71681702021</v>
@@ -2854,7 +2854,7 @@
         <v>14713.18038652536</v>
       </c>
       <c r="H38" t="n">
-        <v>14381.73615581552</v>
+        <v>14381.73615581553</v>
       </c>
       <c r="I38" t="n">
         <v>20292.03029497925</v>
@@ -2872,7 +2872,7 @@
         <v>18349.42376968198</v>
       </c>
       <c r="N38" t="n">
-        <v>18692.03282830083</v>
+        <v>18692.03282830084</v>
       </c>
       <c r="O38" t="n">
         <v>24329.32850854192</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10597.62338503174</v>
+        <v>10597.62338503173</v>
       </c>
       <c r="D39" t="n">
         <v>10554.29646696171</v>
@@ -2924,10 +2924,10 @@
         <v>11241.32635604906</v>
       </c>
       <c r="J39" t="n">
-        <v>9243.123559722857</v>
+        <v>9243.123559722855</v>
       </c>
       <c r="K39" t="n">
-        <v>9251.085186949196</v>
+        <v>9251.085186949194</v>
       </c>
       <c r="L39" t="n">
         <v>10446.21230250395</v>
@@ -2954,7 +2954,7 @@
         <v>13969.81432235915</v>
       </c>
       <c r="T39" t="n">
-        <v>15813.13354773164</v>
+        <v>15813.13354773165</v>
       </c>
     </row>
     <row r="40">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5424.772336039508</v>
+        <v>5424.772336039509</v>
       </c>
       <c r="D40" t="n">
         <v>4032.597016052911</v>
@@ -2988,10 +2988,10 @@
         <v>6103.478441901705</v>
       </c>
       <c r="J40" t="n">
-        <v>5256.664328213623</v>
+        <v>5256.664328213622</v>
       </c>
       <c r="K40" t="n">
-        <v>4978.460286698091</v>
+        <v>4978.460286698092</v>
       </c>
       <c r="L40" t="n">
         <v>5688.111520130472</v>
@@ -3015,7 +3015,7 @@
         <v>9746.658755451752</v>
       </c>
       <c r="S40" t="n">
-        <v>9516.318362155418</v>
+        <v>9516.31836215542</v>
       </c>
       <c r="T40" t="n">
         <v>9476.053971934807</v>
@@ -3046,16 +3046,16 @@
         <v>11578.66396010074</v>
       </c>
       <c r="H41" t="n">
-        <v>23540.93901956484</v>
+        <v>23540.93901956483</v>
       </c>
       <c r="I41" t="n">
-        <v>16056.27683906955</v>
+        <v>16056.27683906956</v>
       </c>
       <c r="J41" t="n">
-        <v>13678.00743128774</v>
+        <v>13678.00743128773</v>
       </c>
       <c r="K41" t="n">
-        <v>13928.05789729702</v>
+        <v>13928.05789729703</v>
       </c>
       <c r="L41" t="n">
         <v>21005.81079341986</v>
@@ -3064,7 +3064,7 @@
         <v>15020.45986301169</v>
       </c>
       <c r="N41" t="n">
-        <v>14428.80937351024</v>
+        <v>14428.80937351023</v>
       </c>
       <c r="O41" t="n">
         <v>21283.86944141392</v>
@@ -3073,13 +3073,13 @@
         <v>22159.83625758499</v>
       </c>
       <c r="Q41" t="n">
-        <v>19128.86353516434</v>
+        <v>19128.86353516433</v>
       </c>
       <c r="R41" t="n">
         <v>23949.05095200942</v>
       </c>
       <c r="S41" t="n">
-        <v>22477.05080519096</v>
+        <v>22477.05080519097</v>
       </c>
       <c r="T41" t="n">
         <v>23535.33419702808</v>
@@ -3107,7 +3107,7 @@
         <v>25020.04521797466</v>
       </c>
       <c r="G42" t="n">
-        <v>26806.63807864148</v>
+        <v>26806.63807864149</v>
       </c>
       <c r="H42" t="n">
         <v>31286.02253367831</v>
@@ -3116,13 +3116,13 @@
         <v>35124.37787222382</v>
       </c>
       <c r="J42" t="n">
-        <v>28828.51404545522</v>
+        <v>28828.51404545523</v>
       </c>
       <c r="K42" t="n">
         <v>29210.42634216896</v>
       </c>
       <c r="L42" t="n">
-        <v>36512.13935168049</v>
+        <v>36512.1393516805</v>
       </c>
       <c r="M42" t="n">
         <v>30201.03696918103</v>
@@ -3143,7 +3143,7 @@
         <v>42609.22479456379</v>
       </c>
       <c r="S42" t="n">
-        <v>44209.63493873584</v>
+        <v>44209.63493873583</v>
       </c>
       <c r="T42" t="n">
         <v>42033.00542923552</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50023.96759422588</v>
+        <v>50023.96759422589</v>
       </c>
       <c r="D43" t="n">
         <v>41290.67299195355</v>
       </c>
       <c r="E43" t="n">
-        <v>48210.17319831929</v>
+        <v>48210.17319831927</v>
       </c>
       <c r="F43" t="n">
-        <v>37947.41102278997</v>
+        <v>37947.41102278996</v>
       </c>
       <c r="G43" t="n">
-        <v>43704.32383021626</v>
+        <v>43704.32383021627</v>
       </c>
       <c r="H43" t="n">
-        <v>72655.28769452989</v>
+        <v>72655.28769452986</v>
       </c>
       <c r="I43" t="n">
-        <v>74653.80770451539</v>
+        <v>74653.80770451541</v>
       </c>
       <c r="J43" t="n">
-        <v>57646.57828371993</v>
+        <v>57646.57828371991</v>
       </c>
       <c r="K43" t="n">
-        <v>68933.02210134691</v>
+        <v>68933.02210134693</v>
       </c>
       <c r="L43" t="n">
-        <v>73133.99523625961</v>
+        <v>73133.99523625965</v>
       </c>
       <c r="M43" t="n">
-        <v>68397.23823608116</v>
+        <v>68397.23823608115</v>
       </c>
       <c r="N43" t="n">
-        <v>68982.15115821449</v>
+        <v>68982.15115821447</v>
       </c>
       <c r="O43" t="n">
         <v>119678.5090075015</v>
@@ -3226,7 +3226,7 @@
         <v>356283.6009509133</v>
       </c>
       <c r="D44" t="n">
-        <v>301909.4677237959</v>
+        <v>301909.4677237958</v>
       </c>
       <c r="E44" t="n">
         <v>278070.266252168</v>
@@ -3238,16 +3238,16 @@
         <v>278893.6876172047</v>
       </c>
       <c r="H44" t="n">
-        <v>293950.3865704216</v>
+        <v>293950.3865704214</v>
       </c>
       <c r="I44" t="n">
         <v>409230.4448626505</v>
       </c>
       <c r="J44" t="n">
-        <v>358771.2298148252</v>
+        <v>358771.2298148253</v>
       </c>
       <c r="K44" t="n">
-        <v>368935.1407976839</v>
+        <v>368935.140797684</v>
       </c>
       <c r="L44" t="n">
         <v>398844.2478445019</v>
@@ -3262,19 +3262,19 @@
         <v>603311.912742639</v>
       </c>
       <c r="P44" t="n">
-        <v>639199.0527415283</v>
+        <v>639199.052741528</v>
       </c>
       <c r="Q44" t="n">
-        <v>620591.2985391356</v>
+        <v>620591.2985391354</v>
       </c>
       <c r="R44" t="n">
-        <v>672934.3925760589</v>
+        <v>672934.3925760586</v>
       </c>
       <c r="S44" t="n">
-        <v>765938.7722344897</v>
+        <v>765938.7722344899</v>
       </c>
       <c r="T44" t="n">
-        <v>791479.0836462835</v>
+        <v>791479.0836462833</v>
       </c>
     </row>
     <row r="45">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9030.765171148194</v>
+        <v>9030.765171148196</v>
       </c>
       <c r="D45" t="n">
-        <v>7767.029141550843</v>
+        <v>7767.029141550844</v>
       </c>
       <c r="E45" t="n">
         <v>7709.842788113909</v>
@@ -3302,7 +3302,7 @@
         <v>6208.350952867429</v>
       </c>
       <c r="H45" t="n">
-        <v>6165.965339319712</v>
+        <v>6165.965339319711</v>
       </c>
       <c r="I45" t="n">
         <v>10351.93516762994</v>
@@ -3311,7 +3311,7 @@
         <v>8854.450462118861</v>
       </c>
       <c r="K45" t="n">
-        <v>9952.359966913955</v>
+        <v>9952.359966913957</v>
       </c>
       <c r="L45" t="n">
         <v>10624.22753944017</v>
@@ -3378,16 +3378,16 @@
         <v>2461.497180392417</v>
       </c>
       <c r="L46" t="n">
-        <v>2645.573870998329</v>
+        <v>2645.573870998328</v>
       </c>
       <c r="M46" t="n">
         <v>2544.934800537666</v>
       </c>
       <c r="N46" t="n">
-        <v>2823.600547836104</v>
+        <v>2823.600547836103</v>
       </c>
       <c r="O46" t="n">
-        <v>3228.434537885339</v>
+        <v>3228.43453788534</v>
       </c>
       <c r="P46" t="n">
         <v>3037.819253975631</v>
@@ -3421,13 +3421,13 @@
         <v>10976.96091750392</v>
       </c>
       <c r="E47" t="n">
-        <v>8467.407633152137</v>
+        <v>8467.407633152139</v>
       </c>
       <c r="F47" t="n">
         <v>7179.717950597004</v>
       </c>
       <c r="G47" t="n">
-        <v>7494.776857486654</v>
+        <v>7494.776857486655</v>
       </c>
       <c r="H47" t="n">
         <v>8061.996704798839</v>
@@ -3436,16 +3436,16 @@
         <v>10067.6511593211</v>
       </c>
       <c r="J47" t="n">
-        <v>8392.059899372729</v>
+        <v>8392.059899372731</v>
       </c>
       <c r="K47" t="n">
-        <v>7293.269896250807</v>
+        <v>7293.269896250808</v>
       </c>
       <c r="L47" t="n">
         <v>9086.754597285879</v>
       </c>
       <c r="M47" t="n">
-        <v>8745.519302797913</v>
+        <v>8745.519302797915</v>
       </c>
       <c r="N47" t="n">
         <v>9410.268049797709</v>
@@ -3506,10 +3506,10 @@
         <v>176395.7247338111</v>
       </c>
       <c r="L48" t="n">
-        <v>165385.1389678194</v>
+        <v>165385.1389678195</v>
       </c>
       <c r="M48" t="n">
-        <v>167362.0192092196</v>
+        <v>167362.0192092197</v>
       </c>
       <c r="N48" t="n">
         <v>168526.6279373866</v>
@@ -3518,7 +3518,7 @@
         <v>269129.0708401785</v>
       </c>
       <c r="P48" t="n">
-        <v>284032.7742151313</v>
+        <v>284032.7742151314</v>
       </c>
       <c r="Q48" t="n">
         <v>243322.1739642005</v>
@@ -3610,37 +3610,37 @@
         <v>6665.764841091598</v>
       </c>
       <c r="D50" t="n">
-        <v>5503.472560037606</v>
+        <v>5503.472560037604</v>
       </c>
       <c r="E50" t="n">
-        <v>6390.892961825272</v>
+        <v>6390.892961825273</v>
       </c>
       <c r="F50" t="n">
-        <v>4753.912566965467</v>
+        <v>4753.912566965468</v>
       </c>
       <c r="G50" t="n">
         <v>4700.697122076701</v>
       </c>
       <c r="H50" t="n">
-        <v>6871.307698239106</v>
+        <v>6871.307698239107</v>
       </c>
       <c r="I50" t="n">
-        <v>7557.638690687373</v>
+        <v>7557.638690687374</v>
       </c>
       <c r="J50" t="n">
         <v>6380.222080098616</v>
       </c>
       <c r="K50" t="n">
-        <v>6227.869978804895</v>
+        <v>6227.869978804897</v>
       </c>
       <c r="L50" t="n">
-        <v>7814.125788544009</v>
+        <v>7814.125788544008</v>
       </c>
       <c r="M50" t="n">
         <v>7944.246827331061</v>
       </c>
       <c r="N50" t="n">
-        <v>7109.776532267118</v>
+        <v>7109.776532267119</v>
       </c>
       <c r="O50" t="n">
         <v>12322.07862252797</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1540487.00854229</v>
+        <v>1540487.008542291</v>
       </c>
       <c r="D51" t="n">
-        <v>1346502.610241648</v>
+        <v>1346502.610241649</v>
       </c>
       <c r="E51" t="n">
         <v>1341446.536810942</v>
@@ -3689,7 +3689,7 @@
         <v>1630691.845527004</v>
       </c>
       <c r="I51" t="n">
-        <v>1983868.622221386</v>
+        <v>1983868.622221387</v>
       </c>
       <c r="J51" t="n">
         <v>1686510.336158153</v>
@@ -3698,7 +3698,7 @@
         <v>1661449.862586116</v>
       </c>
       <c r="L51" t="n">
-        <v>2185970.841244611</v>
+        <v>2185970.84124461</v>
       </c>
       <c r="M51" t="n">
         <v>2077480.664641293</v>
@@ -3710,19 +3710,19 @@
         <v>4334851.133852703</v>
       </c>
       <c r="P51" t="n">
-        <v>4336460.546780949</v>
+        <v>4336460.546780951</v>
       </c>
       <c r="Q51" t="n">
-        <v>4358329.45606089</v>
+        <v>4358329.456060889</v>
       </c>
       <c r="R51" t="n">
-        <v>6307862.149692723</v>
+        <v>6307862.149692724</v>
       </c>
       <c r="S51" t="n">
         <v>6852210.890353537</v>
       </c>
       <c r="T51" t="n">
-        <v>6453062.967208306</v>
+        <v>6453062.967208308</v>
       </c>
     </row>
     <row r="52">
@@ -3738,7 +3738,7 @@
         <v>13869.23768626173</v>
       </c>
       <c r="D52" t="n">
-        <v>12680.16370937178</v>
+        <v>12680.16370937179</v>
       </c>
       <c r="E52" t="n">
         <v>12304.55348403681</v>
@@ -3780,7 +3780,7 @@
         <v>22269.21252320748</v>
       </c>
       <c r="R52" t="n">
-        <v>24211.89943674033</v>
+        <v>24211.89943674034</v>
       </c>
       <c r="S52" t="n">
         <v>24957.79765693462</v>
@@ -3799,31 +3799,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3716.746669197465</v>
+        <v>3716.746669197466</v>
       </c>
       <c r="D53" t="n">
         <v>3624.207092948436</v>
       </c>
       <c r="E53" t="n">
-        <v>3548.773176059321</v>
+        <v>3548.77317605932</v>
       </c>
       <c r="F53" t="n">
-        <v>2692.521574884991</v>
+        <v>2692.52157488499</v>
       </c>
       <c r="G53" t="n">
-        <v>2790.90946247355</v>
+        <v>2790.909462473551</v>
       </c>
       <c r="H53" t="n">
         <v>3129.812812254926</v>
       </c>
       <c r="I53" t="n">
-        <v>3424.478917272521</v>
+        <v>3424.47891727252</v>
       </c>
       <c r="J53" t="n">
         <v>2823.587833055203</v>
       </c>
       <c r="K53" t="n">
-        <v>2998.883301353799</v>
+        <v>2998.8833013538</v>
       </c>
       <c r="L53" t="n">
         <v>3102.913698279619</v>
@@ -3835,22 +3835,22 @@
         <v>3257.932904984</v>
       </c>
       <c r="O53" t="n">
-        <v>3863.200138757438</v>
+        <v>3863.200138757439</v>
       </c>
       <c r="P53" t="n">
-        <v>4250.694333159995</v>
+        <v>4250.694333159996</v>
       </c>
       <c r="Q53" t="n">
         <v>3686.178443637197</v>
       </c>
       <c r="R53" t="n">
-        <v>3932.906094604693</v>
+        <v>3932.906094604694</v>
       </c>
       <c r="S53" t="n">
         <v>3890.639015342154</v>
       </c>
       <c r="T53" t="n">
-        <v>4588.27779954003</v>
+        <v>4588.277799540031</v>
       </c>
     </row>
     <row r="54">
@@ -3878,16 +3878,16 @@
         <v>1601575.130006436</v>
       </c>
       <c r="H54" t="n">
-        <v>1604797.107410745</v>
+        <v>1604797.107410746</v>
       </c>
       <c r="I54" t="n">
-        <v>2081529.966529311</v>
+        <v>2081529.966529312</v>
       </c>
       <c r="J54" t="n">
-        <v>1726218.01085555</v>
+        <v>1726218.010855551</v>
       </c>
       <c r="K54" t="n">
-        <v>1675498.668482557</v>
+        <v>1675498.668482556</v>
       </c>
       <c r="L54" t="n">
         <v>1773500.618867577</v>
@@ -3899,22 +3899,22 @@
         <v>1921358.047178707</v>
       </c>
       <c r="O54" t="n">
-        <v>4136509.7853063</v>
+        <v>4136509.785306299</v>
       </c>
       <c r="P54" t="n">
-        <v>3512799.669211641</v>
+        <v>3512799.669211642</v>
       </c>
       <c r="Q54" t="n">
-        <v>3489784.792116841</v>
+        <v>3489784.792116842</v>
       </c>
       <c r="R54" t="n">
         <v>4797023.275532433</v>
       </c>
       <c r="S54" t="n">
-        <v>5422082.602885723</v>
+        <v>5422082.602885727</v>
       </c>
       <c r="T54" t="n">
-        <v>5343844.738192338</v>
+        <v>5343844.738192339</v>
       </c>
     </row>
     <row r="55">
@@ -3939,13 +3939,13 @@
         <v>128553.1058571318</v>
       </c>
       <c r="G55" t="n">
-        <v>140961.1873916173</v>
+        <v>140961.1873916172</v>
       </c>
       <c r="H55" t="n">
         <v>188075.8577459102</v>
       </c>
       <c r="I55" t="n">
-        <v>197884.3188666372</v>
+        <v>197884.3188666373</v>
       </c>
       <c r="J55" t="n">
         <v>165808.3754995824</v>
@@ -3954,7 +3954,7 @@
         <v>178354.6196971321</v>
       </c>
       <c r="L55" t="n">
-        <v>179539.6817815367</v>
+        <v>179539.6817815368</v>
       </c>
       <c r="M55" t="n">
         <v>168842.0056868316</v>
@@ -3966,7 +3966,7 @@
         <v>246703.0388375197</v>
       </c>
       <c r="P55" t="n">
-        <v>232299.8167994678</v>
+        <v>232299.8167994677</v>
       </c>
       <c r="Q55" t="n">
         <v>232868.0136247402</v>
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>893246.6160794846</v>
+        <v>893246.6160794847</v>
       </c>
       <c r="D56" t="n">
         <v>791574.5494547825</v>
       </c>
       <c r="E56" t="n">
-        <v>823505.9316523516</v>
+        <v>823505.9316523519</v>
       </c>
       <c r="F56" t="n">
-        <v>857835.0263511793</v>
+        <v>857835.0263511788</v>
       </c>
       <c r="G56" t="n">
-        <v>896260.0861103545</v>
+        <v>896260.0861103544</v>
       </c>
       <c r="H56" t="n">
-        <v>907628.7263514047</v>
+        <v>907628.7263514046</v>
       </c>
       <c r="I56" t="n">
         <v>1385726.823825609</v>
       </c>
       <c r="J56" t="n">
-        <v>1170751.453967221</v>
+        <v>1170751.45396722</v>
       </c>
       <c r="K56" t="n">
         <v>1256779.022954656</v>
@@ -4036,13 +4036,13 @@
         <v>1614831.241620482</v>
       </c>
       <c r="R56" t="n">
-        <v>1740614.797307316</v>
+        <v>1740614.797307315</v>
       </c>
       <c r="S56" t="n">
         <v>1924582.852924438</v>
       </c>
       <c r="T56" t="n">
-        <v>2105742.373600753</v>
+        <v>2105742.373600752</v>
       </c>
     </row>
     <row r="57">
@@ -4128,10 +4128,10 @@
         <v>25406.57337053356</v>
       </c>
       <c r="F58" t="n">
-        <v>22229.15699663668</v>
+        <v>22229.15699663669</v>
       </c>
       <c r="G58" t="n">
-        <v>24379.27694653333</v>
+        <v>24379.27694653332</v>
       </c>
       <c r="H58" t="n">
         <v>16631.52530886114</v>
@@ -4140,13 +4140,13 @@
         <v>28977.70196159949</v>
       </c>
       <c r="J58" t="n">
-        <v>23695.65978384287</v>
+        <v>23695.65978384288</v>
       </c>
       <c r="K58" t="n">
         <v>25013.17838507153</v>
       </c>
       <c r="L58" t="n">
-        <v>26878.12435472079</v>
+        <v>26878.1243547208</v>
       </c>
       <c r="M58" t="n">
         <v>24781.50296424874</v>
@@ -4164,10 +4164,10 @@
         <v>34571.03684308938</v>
       </c>
       <c r="R58" t="n">
-        <v>33911.17028253476</v>
+        <v>33911.17028253477</v>
       </c>
       <c r="S58" t="n">
-        <v>37173.41452407321</v>
+        <v>37173.41452407322</v>
       </c>
       <c r="T58" t="n">
         <v>37699.46633778473</v>
@@ -4186,7 +4186,7 @@
         <v>27848.37566862792</v>
       </c>
       <c r="D59" t="n">
-        <v>20019.13292066159</v>
+        <v>20019.13292066158</v>
       </c>
       <c r="E59" t="n">
         <v>24926.75873159415</v>
@@ -4198,16 +4198,16 @@
         <v>23423.6048947681</v>
       </c>
       <c r="H59" t="n">
-        <v>32689.3102910589</v>
+        <v>32689.31029105889</v>
       </c>
       <c r="I59" t="n">
-        <v>33208.87036579628</v>
+        <v>33208.87036579629</v>
       </c>
       <c r="J59" t="n">
-        <v>31799.40480777028</v>
+        <v>31799.40480777029</v>
       </c>
       <c r="K59" t="n">
-        <v>29159.32638278109</v>
+        <v>29159.3263827811</v>
       </c>
       <c r="L59" t="n">
         <v>31201.77920340443</v>
@@ -4216,25 +4216,25 @@
         <v>31271.06746958207</v>
       </c>
       <c r="N59" t="n">
-        <v>30097.30098174731</v>
+        <v>30097.30098174732</v>
       </c>
       <c r="O59" t="n">
-        <v>41069.35717235432</v>
+        <v>41069.35717235433</v>
       </c>
       <c r="P59" t="n">
-        <v>42681.02134644192</v>
+        <v>42681.02134644191</v>
       </c>
       <c r="Q59" t="n">
         <v>40036.01183295812</v>
       </c>
       <c r="R59" t="n">
-        <v>50569.56665795493</v>
+        <v>50569.56665795494</v>
       </c>
       <c r="S59" t="n">
         <v>42148.37521517064</v>
       </c>
       <c r="T59" t="n">
-        <v>47391.36386808343</v>
+        <v>47391.36386808344</v>
       </c>
     </row>
     <row r="60">
@@ -4256,7 +4256,7 @@
         <v>242751.1363227099</v>
       </c>
       <c r="F60" t="n">
-        <v>244440.6550825785</v>
+        <v>244440.6550825784</v>
       </c>
       <c r="G60" t="n">
         <v>239965.4543040615</v>
@@ -4265,34 +4265,34 @@
         <v>287365.1180771266</v>
       </c>
       <c r="I60" t="n">
-        <v>378237.163788957</v>
+        <v>378237.1637889569</v>
       </c>
       <c r="J60" t="n">
         <v>330785.9521814676</v>
       </c>
       <c r="K60" t="n">
-        <v>332487.1377409805</v>
+        <v>332487.1377409804</v>
       </c>
       <c r="L60" t="n">
-        <v>354547.4303322049</v>
+        <v>354547.430332205</v>
       </c>
       <c r="M60" t="n">
         <v>342615.2326800064</v>
       </c>
       <c r="N60" t="n">
-        <v>371174.287070474</v>
+        <v>371174.2870704739</v>
       </c>
       <c r="O60" t="n">
-        <v>450208.5831871569</v>
+        <v>450208.5831871568</v>
       </c>
       <c r="P60" t="n">
         <v>443275.8968813916</v>
       </c>
       <c r="Q60" t="n">
-        <v>457131.4586588208</v>
+        <v>457131.4586588207</v>
       </c>
       <c r="R60" t="n">
-        <v>497377.9278432563</v>
+        <v>497377.9278432562</v>
       </c>
       <c r="S60" t="n">
         <v>512754.9117831817</v>
@@ -4329,7 +4329,7 @@
         <v>18211.48945687795</v>
       </c>
       <c r="I61" t="n">
-        <v>21495.76052481032</v>
+        <v>21495.76052481033</v>
       </c>
       <c r="J61" t="n">
         <v>18677.41342296225</v>
@@ -4341,10 +4341,10 @@
         <v>18157.36569003742</v>
       </c>
       <c r="M61" t="n">
-        <v>17666.61752572235</v>
+        <v>17666.61752572236</v>
       </c>
       <c r="N61" t="n">
-        <v>17593.58680014723</v>
+        <v>17593.58680014722</v>
       </c>
       <c r="O61" t="n">
         <v>24123.88475304773</v>
@@ -4359,10 +4359,10 @@
         <v>35280.48692744078</v>
       </c>
       <c r="S61" t="n">
-        <v>38506.17626960874</v>
+        <v>38506.17626960875</v>
       </c>
       <c r="T61" t="n">
-        <v>33495.59124264168</v>
+        <v>33495.59124264169</v>
       </c>
     </row>
     <row r="62">
@@ -4378,7 +4378,7 @@
         <v>4711.534641075562</v>
       </c>
       <c r="D62" t="n">
-        <v>296.5543640067404</v>
+        <v>296.5543640067405</v>
       </c>
       <c r="E62" t="n">
         <v>4723.68682037278</v>
@@ -4454,7 +4454,7 @@
         <v>405688.3697695227</v>
       </c>
       <c r="H63" t="n">
-        <v>491307.7117642088</v>
+        <v>491307.7117642087</v>
       </c>
       <c r="I63" t="n">
         <v>453691.7683346702</v>
@@ -4463,7 +4463,7 @@
         <v>419799.5837570635</v>
       </c>
       <c r="K63" t="n">
-        <v>408965.8518321534</v>
+        <v>408965.8518321533</v>
       </c>
       <c r="L63" t="n">
         <v>345243.8676791553</v>
@@ -4472,13 +4472,13 @@
         <v>364923.2608524072</v>
       </c>
       <c r="N63" t="n">
-        <v>420597.5334905485</v>
+        <v>420597.5334905484</v>
       </c>
       <c r="O63" t="n">
         <v>376288.2312034492</v>
       </c>
       <c r="P63" t="n">
-        <v>380140.4012778322</v>
+        <v>380140.4012778321</v>
       </c>
       <c r="Q63" t="n">
         <v>325465.8085271202</v>
@@ -4487,7 +4487,7 @@
         <v>418488.1296403339</v>
       </c>
       <c r="S63" t="n">
-        <v>426554.022706711</v>
+        <v>426554.0227067111</v>
       </c>
       <c r="T63" t="n">
         <v>367838.8624452599</v>
@@ -4533,7 +4533,7 @@
         <v>4009.864169577484</v>
       </c>
       <c r="M64" t="n">
-        <v>4097.030430783816</v>
+        <v>4097.030430783815</v>
       </c>
       <c r="N64" t="n">
         <v>4037.466253496553</v>
@@ -4582,16 +4582,16 @@
         <v>547867.9732438761</v>
       </c>
       <c r="H65" t="n">
-        <v>849928.1131370188</v>
+        <v>849928.1131370189</v>
       </c>
       <c r="I65" t="n">
-        <v>785321.3354572543</v>
+        <v>785321.3354572544</v>
       </c>
       <c r="J65" t="n">
-        <v>680374.3288331603</v>
+        <v>680374.3288331606</v>
       </c>
       <c r="K65" t="n">
-        <v>705571.235179388</v>
+        <v>705571.2351793877</v>
       </c>
       <c r="L65" t="n">
         <v>756529.9533777571</v>
@@ -4600,7 +4600,7 @@
         <v>726015.7370209511</v>
       </c>
       <c r="N65" t="n">
-        <v>742452.4095966573</v>
+        <v>742452.4095966571</v>
       </c>
       <c r="O65" t="n">
         <v>1109194.951625529</v>
@@ -4609,7 +4609,7 @@
         <v>1133022.265923282</v>
       </c>
       <c r="Q65" t="n">
-        <v>969021.1036572377</v>
+        <v>969021.103657238</v>
       </c>
       <c r="R65" t="n">
         <v>1262529.967991586</v>
@@ -4631,34 +4631,34 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>44596.9314757802</v>
+        <v>44596.93147578018</v>
       </c>
       <c r="D66" t="n">
         <v>38188.1021264232</v>
       </c>
       <c r="E66" t="n">
-        <v>39100.3676425074</v>
+        <v>39100.36764250739</v>
       </c>
       <c r="F66" t="n">
         <v>34213.9815707767</v>
       </c>
       <c r="G66" t="n">
-        <v>36712.38475948927</v>
+        <v>36712.38475948926</v>
       </c>
       <c r="H66" t="n">
         <v>50168.80776533965</v>
       </c>
       <c r="I66" t="n">
-        <v>59112.83049306937</v>
+        <v>59112.83049306938</v>
       </c>
       <c r="J66" t="n">
-        <v>50356.42892315912</v>
+        <v>50356.42892315913</v>
       </c>
       <c r="K66" t="n">
         <v>50540.9873160037</v>
       </c>
       <c r="L66" t="n">
-        <v>50989.41645101442</v>
+        <v>50989.41645101441</v>
       </c>
       <c r="M66" t="n">
         <v>51212.40781203928</v>
@@ -4667,10 +4667,10 @@
         <v>50393.10476082179</v>
       </c>
       <c r="O66" t="n">
-        <v>76401.30075394324</v>
+        <v>76401.30075394326</v>
       </c>
       <c r="P66" t="n">
-        <v>73987.03569518086</v>
+        <v>73987.03569518088</v>
       </c>
       <c r="Q66" t="n">
         <v>76762.6911881088</v>
@@ -4679,7 +4679,7 @@
         <v>88348.46340091429</v>
       </c>
       <c r="S66" t="n">
-        <v>87970.40874056677</v>
+        <v>87970.40874056678</v>
       </c>
       <c r="T66" t="n">
         <v>80838.91001508871</v>
@@ -4704,10 +4704,10 @@
         <v>1046.899143797399</v>
       </c>
       <c r="F67" t="n">
-        <v>866.7065623855409</v>
+        <v>866.7065623855408</v>
       </c>
       <c r="G67" t="n">
-        <v>920.3827195808718</v>
+        <v>920.3827195808719</v>
       </c>
       <c r="H67" t="n">
         <v>885.2364519753107</v>
@@ -4719,16 +4719,16 @@
         <v>858.505833831831</v>
       </c>
       <c r="K67" t="n">
-        <v>987.0361571950331</v>
+        <v>987.036157195033</v>
       </c>
       <c r="L67" t="n">
-        <v>959.5281423175072</v>
+        <v>959.5281423175073</v>
       </c>
       <c r="M67" t="n">
-        <v>892.5517668181797</v>
+        <v>892.5517668181795</v>
       </c>
       <c r="N67" t="n">
-        <v>964.1651166130985</v>
+        <v>964.1651166130983</v>
       </c>
       <c r="O67" t="n">
         <v>1101.122568481098</v>
@@ -4740,7 +4740,7 @@
         <v>1067.734801616014</v>
       </c>
       <c r="R67" t="n">
-        <v>1233.563303395791</v>
+        <v>1233.56330339579</v>
       </c>
       <c r="S67" t="n">
         <v>1137.361271502524</v>
@@ -4762,31 +4762,31 @@
         <v>7337.763616511563</v>
       </c>
       <c r="D68" t="n">
-        <v>7118.023067319684</v>
+        <v>7118.023067319682</v>
       </c>
       <c r="E68" t="n">
-        <v>6611.056192466137</v>
+        <v>6611.056192466136</v>
       </c>
       <c r="F68" t="n">
-        <v>5923.349619537802</v>
+        <v>5923.349619537801</v>
       </c>
       <c r="G68" t="n">
-        <v>5992.287389674708</v>
+        <v>5992.28738967471</v>
       </c>
       <c r="H68" t="n">
-        <v>6733.717507541001</v>
+        <v>6733.717507541</v>
       </c>
       <c r="I68" t="n">
-        <v>9142.084276512656</v>
+        <v>9142.084276512653</v>
       </c>
       <c r="J68" t="n">
         <v>7222.600632271921</v>
       </c>
       <c r="K68" t="n">
-        <v>8304.439167392735</v>
+        <v>8304.439167392733</v>
       </c>
       <c r="L68" t="n">
-        <v>8353.510737477192</v>
+        <v>8353.510737477194</v>
       </c>
       <c r="M68" t="n">
         <v>7580.602333938078</v>
@@ -4807,7 +4807,7 @@
         <v>12098.85853570209</v>
       </c>
       <c r="S68" t="n">
-        <v>13548.17133899828</v>
+        <v>13548.17133899829</v>
       </c>
       <c r="T68" t="n">
         <v>14528.42708711926</v>
@@ -4826,7 +4826,7 @@
         <v>15235.81002464159</v>
       </c>
       <c r="D69" t="n">
-        <v>12357.99351415609</v>
+        <v>12357.99351415608</v>
       </c>
       <c r="E69" t="n">
         <v>11119.6422232687</v>
@@ -4841,10 +4841,10 @@
         <v>18256.93344441742</v>
       </c>
       <c r="I69" t="n">
-        <v>21548.79896836336</v>
+        <v>21548.79896836335</v>
       </c>
       <c r="J69" t="n">
-        <v>19014.27951564364</v>
+        <v>19014.27951564363</v>
       </c>
       <c r="K69" t="n">
         <v>17734.6663182427</v>
@@ -4954,34 +4954,34 @@
         <v>835702.0846413946</v>
       </c>
       <c r="D71" t="n">
-        <v>831587.0020042546</v>
+        <v>831587.0020042548</v>
       </c>
       <c r="E71" t="n">
-        <v>972530.490078805</v>
+        <v>972530.4900788051</v>
       </c>
       <c r="F71" t="n">
         <v>570529.8979327879</v>
       </c>
       <c r="G71" t="n">
-        <v>635803.5582362354</v>
+        <v>635803.5582362353</v>
       </c>
       <c r="H71" t="n">
-        <v>641796.6893233313</v>
+        <v>641796.6893233312</v>
       </c>
       <c r="I71" t="n">
-        <v>808745.2941124557</v>
+        <v>808745.2941124556</v>
       </c>
       <c r="J71" t="n">
-        <v>687563.737446527</v>
+        <v>687563.7374465269</v>
       </c>
       <c r="K71" t="n">
-        <v>683167.4549330447</v>
+        <v>683167.4549330446</v>
       </c>
       <c r="L71" t="n">
         <v>693857.2250223815</v>
       </c>
       <c r="M71" t="n">
-        <v>652888.0686670622</v>
+        <v>652888.0686670621</v>
       </c>
       <c r="N71" t="n">
         <v>737876.378935673</v>
@@ -4990,16 +4990,16 @@
         <v>753389.1968128966</v>
       </c>
       <c r="P71" t="n">
-        <v>736616.4872700069</v>
+        <v>736616.487270007</v>
       </c>
       <c r="Q71" t="n">
-        <v>702709.9986654156</v>
+        <v>702709.9986654158</v>
       </c>
       <c r="R71" t="n">
         <v>759202.3832994337</v>
       </c>
       <c r="S71" t="n">
-        <v>807854.2111324484</v>
+        <v>807854.2111324483</v>
       </c>
       <c r="T71" t="n">
         <v>819562.6972969892</v>
@@ -5024,7 +5024,7 @@
         <v>118450.7264366685</v>
       </c>
       <c r="F72" t="n">
-        <v>102409.2603991648</v>
+        <v>102409.2603991649</v>
       </c>
       <c r="G72" t="n">
         <v>100307.036985012</v>
@@ -5054,10 +5054,10 @@
         <v>246596.9081805854</v>
       </c>
       <c r="P72" t="n">
-        <v>257502.6190505603</v>
+        <v>257502.6190505602</v>
       </c>
       <c r="Q72" t="n">
-        <v>214269.0590066164</v>
+        <v>214269.0590066165</v>
       </c>
       <c r="R72" t="n">
         <v>286874.3401379299</v>
@@ -5088,10 +5088,10 @@
         <v>103566.5983550936</v>
       </c>
       <c r="F73" t="n">
-        <v>85411.97847383915</v>
+        <v>85411.97847383912</v>
       </c>
       <c r="G73" t="n">
-        <v>90898.48922862914</v>
+        <v>90898.48922862916</v>
       </c>
       <c r="H73" t="n">
         <v>120713.9880591943</v>
@@ -5118,10 +5118,10 @@
         <v>157382.8397104098</v>
       </c>
       <c r="P73" t="n">
-        <v>169902.9930418215</v>
+        <v>169902.9930418214</v>
       </c>
       <c r="Q73" t="n">
-        <v>151914.2699583096</v>
+        <v>151914.2699583097</v>
       </c>
       <c r="R73" t="n">
         <v>173991.849242616</v>
@@ -5152,10 +5152,10 @@
         <v>121164.5371196253</v>
       </c>
       <c r="F74" t="n">
-        <v>88058.83825806425</v>
+        <v>88058.83825806426</v>
       </c>
       <c r="G74" t="n">
-        <v>92896.73910330344</v>
+        <v>92896.73910330345</v>
       </c>
       <c r="H74" t="n">
         <v>165080.9161766719</v>
@@ -5179,16 +5179,16 @@
         <v>129777.3367821401</v>
       </c>
       <c r="O74" t="n">
-        <v>180752.050162347</v>
+        <v>180752.0501623471</v>
       </c>
       <c r="P74" t="n">
-        <v>183659.6514588697</v>
+        <v>183659.6514588698</v>
       </c>
       <c r="Q74" t="n">
-        <v>157978.3474200688</v>
+        <v>157978.3474200687</v>
       </c>
       <c r="R74" t="n">
-        <v>192874.7459443134</v>
+        <v>192874.7459443133</v>
       </c>
       <c r="S74" t="n">
         <v>185356.5397182008</v>
@@ -5258,7 +5258,7 @@
         <v>351.5658827399686</v>
       </c>
       <c r="T75" t="n">
-        <v>376.5444477092277</v>
+        <v>376.5444477092276</v>
       </c>
     </row>
     <row r="76">
@@ -5274,34 +5274,34 @@
         <v>102879.1465744745</v>
       </c>
       <c r="D76" t="n">
-        <v>89979.31517888652</v>
+        <v>89979.31517888651</v>
       </c>
       <c r="E76" t="n">
         <v>84946.428935822</v>
       </c>
       <c r="F76" t="n">
-        <v>76045.35862049399</v>
+        <v>76045.35862049398</v>
       </c>
       <c r="G76" t="n">
-        <v>75704.51969520068</v>
+        <v>75704.51969520071</v>
       </c>
       <c r="H76" t="n">
-        <v>63564.00177462874</v>
+        <v>63564.00177462875</v>
       </c>
       <c r="I76" t="n">
         <v>114258.0960960094</v>
       </c>
       <c r="J76" t="n">
-        <v>97133.83904681068</v>
+        <v>97133.8390468107</v>
       </c>
       <c r="K76" t="n">
-        <v>99604.57011683055</v>
+        <v>99604.57011683057</v>
       </c>
       <c r="L76" t="n">
         <v>102872.736335685</v>
       </c>
       <c r="M76" t="n">
-        <v>93697.96087737015</v>
+        <v>93697.96087737016</v>
       </c>
       <c r="N76" t="n">
         <v>100718.5049831534</v>
@@ -5313,7 +5313,7 @@
         <v>154981.7692722105</v>
       </c>
       <c r="Q76" t="n">
-        <v>148737.6114622619</v>
+        <v>148737.6114622618</v>
       </c>
       <c r="R76" t="n">
         <v>163250.4356412829</v>
@@ -5475,7 +5475,7 @@
         <v>1297.222475196941</v>
       </c>
       <c r="G79" t="n">
-        <v>1307.100272457083</v>
+        <v>1307.100272457082</v>
       </c>
       <c r="H79" t="n">
         <v>974.3467352468983</v>
@@ -5496,25 +5496,25 @@
         <v>1565.662452997423</v>
       </c>
       <c r="N79" t="n">
-        <v>1777.410280133713</v>
+        <v>1777.410280133712</v>
       </c>
       <c r="O79" t="n">
         <v>2190.111369580614</v>
       </c>
       <c r="P79" t="n">
-        <v>2182.843641529545</v>
+        <v>2182.843641529544</v>
       </c>
       <c r="Q79" t="n">
-        <v>2104.449770991958</v>
+        <v>2104.449770991957</v>
       </c>
       <c r="R79" t="n">
         <v>2328.429913063866</v>
       </c>
       <c r="S79" t="n">
-        <v>2307.893301020313</v>
+        <v>2307.893301020314</v>
       </c>
       <c r="T79" t="n">
-        <v>2370.798556498808</v>
+        <v>2370.798556498807</v>
       </c>
     </row>
     <row r="80">
@@ -5536,10 +5536,10 @@
         <v>8633.341119395849</v>
       </c>
       <c r="F80" t="n">
-        <v>8728.645206022524</v>
+        <v>8728.645206022526</v>
       </c>
       <c r="G80" t="n">
-        <v>8469.028743640356</v>
+        <v>8469.028743640354</v>
       </c>
       <c r="H80" t="n">
         <v>13550.38087131193</v>
@@ -5575,7 +5575,7 @@
         <v>31727.76712539203</v>
       </c>
       <c r="S80" t="n">
-        <v>34353.66431400044</v>
+        <v>34353.66431400045</v>
       </c>
       <c r="T80" t="n">
         <v>30500.57852036048</v>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7567.864719484815</v>
+        <v>7567.864719484814</v>
       </c>
       <c r="D81" t="n">
         <v>7258.579567240198</v>
@@ -5600,31 +5600,31 @@
         <v>7474.265912490568</v>
       </c>
       <c r="F81" t="n">
-        <v>4756.963942055591</v>
+        <v>4756.96394205559</v>
       </c>
       <c r="G81" t="n">
-        <v>5031.627517651569</v>
+        <v>5031.627517651568</v>
       </c>
       <c r="H81" t="n">
-        <v>7129.601119680827</v>
+        <v>7129.601119680828</v>
       </c>
       <c r="I81" t="n">
         <v>6550.884314616313</v>
       </c>
       <c r="J81" t="n">
-        <v>5649.211005794164</v>
+        <v>5649.211005794165</v>
       </c>
       <c r="K81" t="n">
         <v>6006.219408148901</v>
       </c>
       <c r="L81" t="n">
-        <v>6051.721320595743</v>
+        <v>6051.721320595744</v>
       </c>
       <c r="M81" t="n">
         <v>6000.201996610941</v>
       </c>
       <c r="N81" t="n">
-        <v>6553.700897493838</v>
+        <v>6553.700897493839</v>
       </c>
       <c r="O81" t="n">
         <v>8115.180144456189</v>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10569.80309878993</v>
+        <v>10569.80309878992</v>
       </c>
       <c r="D82" t="n">
         <v>9748.6309052044</v>
       </c>
       <c r="E82" t="n">
-        <v>9699.161360244685</v>
+        <v>9699.161360244687</v>
       </c>
       <c r="F82" t="n">
         <v>9987.946962177668</v>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>94221.81344167571</v>
+        <v>94221.81344167569</v>
       </c>
       <c r="D83" t="n">
         <v>86713.40614713149</v>
@@ -5728,10 +5728,10 @@
         <v>86766.95958947654</v>
       </c>
       <c r="F83" t="n">
-        <v>93056.92701822023</v>
+        <v>93056.92701822022</v>
       </c>
       <c r="G83" t="n">
-        <v>95297.4832794994</v>
+        <v>95297.48327949939</v>
       </c>
       <c r="H83" t="n">
         <v>118519.7384554443</v>
@@ -5789,16 +5789,16 @@
         <v>19452.6515435124</v>
       </c>
       <c r="E84" t="n">
-        <v>22942.35720602598</v>
+        <v>22942.35720602599</v>
       </c>
       <c r="F84" t="n">
-        <v>19294.21548135827</v>
+        <v>19294.21548135826</v>
       </c>
       <c r="G84" t="n">
         <v>20774.8925709918</v>
       </c>
       <c r="H84" t="n">
-        <v>36756.54069566362</v>
+        <v>36756.54069566361</v>
       </c>
       <c r="I84" t="n">
         <v>34183.21542628811</v>
@@ -5810,10 +5810,10 @@
         <v>29215.13723348006</v>
       </c>
       <c r="L84" t="n">
-        <v>33884.78429058756</v>
+        <v>33884.78429058754</v>
       </c>
       <c r="M84" t="n">
-        <v>34555.67995030599</v>
+        <v>34555.67995030598</v>
       </c>
       <c r="N84" t="n">
         <v>33221.37030118969</v>
@@ -5825,10 +5825,10 @@
         <v>59136.91155785703</v>
       </c>
       <c r="Q84" t="n">
-        <v>52336.00747523075</v>
+        <v>52336.00747523074</v>
       </c>
       <c r="R84" t="n">
-        <v>61907.647335435</v>
+        <v>61907.64733543499</v>
       </c>
       <c r="S84" t="n">
         <v>74099.78577166141</v>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>72091.55545053222</v>
+        <v>72091.55545053224</v>
       </c>
       <c r="D85" t="n">
         <v>61697.23110795439</v>
@@ -5859,10 +5859,10 @@
         <v>59888.88863581609</v>
       </c>
       <c r="G85" t="n">
-        <v>72343.69837158616</v>
+        <v>72343.69837158617</v>
       </c>
       <c r="H85" t="n">
-        <v>51919.47404602161</v>
+        <v>51919.4740460216</v>
       </c>
       <c r="I85" t="n">
         <v>105388.354858898</v>
@@ -5877,7 +5877,7 @@
         <v>99794.0440734929</v>
       </c>
       <c r="M85" t="n">
-        <v>84304.93752884177</v>
+        <v>84304.93752884178</v>
       </c>
       <c r="N85" t="n">
         <v>102031.667095399</v>
@@ -5889,10 +5889,10 @@
         <v>97073.13424743565</v>
       </c>
       <c r="Q85" t="n">
-        <v>99121.75639882605</v>
+        <v>99121.75639882607</v>
       </c>
       <c r="R85" t="n">
-        <v>82501.17976412442</v>
+        <v>82501.1797641244</v>
       </c>
       <c r="S85" t="n">
         <v>79579.16595580221</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11279.13789873992</v>
+        <v>11279.13789873991</v>
       </c>
       <c r="D86" t="n">
         <v>10668.1197199382</v>
@@ -5956,7 +5956,7 @@
         <v>16563.32691946166</v>
       </c>
       <c r="R86" t="n">
-        <v>20316.74929115595</v>
+        <v>20316.74929115594</v>
       </c>
       <c r="S86" t="n">
         <v>20863.24715956609</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>208780.4718484277</v>
+        <v>208780.4718484278</v>
       </c>
       <c r="D88" t="n">
         <v>205297.0154379632</v>
@@ -6048,13 +6048,13 @@
         <v>229727.8628432061</v>
       </c>
       <c r="F88" t="n">
-        <v>163244.4638113406</v>
+        <v>163244.4638113407</v>
       </c>
       <c r="G88" t="n">
         <v>203057.2862991703</v>
       </c>
       <c r="H88" t="n">
-        <v>156494.3532556938</v>
+        <v>156494.3532556939</v>
       </c>
       <c r="I88" t="n">
         <v>239824.6222327093</v>
@@ -6234,10 +6234,10 @@
         <v>839.824696543547</v>
       </c>
       <c r="D91" t="n">
-        <v>712.1228240861416</v>
+        <v>712.1228240861415</v>
       </c>
       <c r="E91" t="n">
-        <v>769.3143726423563</v>
+        <v>769.3143726423561</v>
       </c>
       <c r="F91" t="n">
         <v>650.030388155533</v>
@@ -6246,22 +6246,22 @@
         <v>746.5252591648918</v>
       </c>
       <c r="H91" t="n">
-        <v>551.5271910475647</v>
+        <v>551.5271910475645</v>
       </c>
       <c r="I91" t="n">
-        <v>862.922199393947</v>
+        <v>862.9221993939469</v>
       </c>
       <c r="J91" t="n">
         <v>722.8550286889536</v>
       </c>
       <c r="K91" t="n">
-        <v>753.6902591359593</v>
+        <v>753.6902591359594</v>
       </c>
       <c r="L91" t="n">
-        <v>933.9920683092251</v>
+        <v>933.9920683092253</v>
       </c>
       <c r="M91" t="n">
-        <v>901.8639848879277</v>
+        <v>901.8639848879276</v>
       </c>
       <c r="N91" t="n">
         <v>968.2698003478897</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8710.030390906375</v>
+        <v>8710.030390906373</v>
       </c>
       <c r="D92" t="n">
         <v>8021.052668371559</v>
@@ -6307,19 +6307,19 @@
         <v>6488.107745878358</v>
       </c>
       <c r="G92" t="n">
-        <v>7314.233884569721</v>
+        <v>7314.23388456972</v>
       </c>
       <c r="H92" t="n">
         <v>5939.201889736192</v>
       </c>
       <c r="I92" t="n">
-        <v>9214.361051948223</v>
+        <v>9214.361051948221</v>
       </c>
       <c r="J92" t="n">
         <v>8385.42855055464</v>
       </c>
       <c r="K92" t="n">
-        <v>8809.429038276017</v>
+        <v>8809.429038276015</v>
       </c>
       <c r="L92" t="n">
         <v>9836.803240440175</v>
@@ -6346,7 +6346,7 @@
         <v>14925.46429897417</v>
       </c>
       <c r="T92" t="n">
-        <v>17137.83858199883</v>
+        <v>17137.83858199882</v>
       </c>
     </row>
     <row r="93">
@@ -6368,7 +6368,7 @@
         <v>106927.1620330789</v>
       </c>
       <c r="F93" t="n">
-        <v>70068.15844585713</v>
+        <v>70068.15844585712</v>
       </c>
       <c r="G93" t="n">
         <v>74758.66005672145</v>
@@ -6389,7 +6389,7 @@
         <v>98497.50308322154</v>
       </c>
       <c r="M93" t="n">
-        <v>94234.94766393681</v>
+        <v>94234.94766393682</v>
       </c>
       <c r="N93" t="n">
         <v>102458.1358827291</v>
@@ -6423,19 +6423,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47893.87254419415</v>
+        <v>47893.87254419414</v>
       </c>
       <c r="D94" t="n">
         <v>49386.46055825801</v>
       </c>
       <c r="E94" t="n">
-        <v>43586.15237497246</v>
+        <v>43586.15237497245</v>
       </c>
       <c r="F94" t="n">
         <v>31047.25422730773</v>
       </c>
       <c r="G94" t="n">
-        <v>35068.58887133343</v>
+        <v>35068.58887133342</v>
       </c>
       <c r="H94" t="n">
         <v>22765.73522100561</v>
@@ -6444,10 +6444,10 @@
         <v>39560.28582021957</v>
       </c>
       <c r="J94" t="n">
-        <v>32820.00920317689</v>
+        <v>32820.0092031769</v>
       </c>
       <c r="K94" t="n">
-        <v>37078.1742132346</v>
+        <v>37078.17421323461</v>
       </c>
       <c r="L94" t="n">
         <v>38686.66082086445</v>
@@ -6462,7 +6462,7 @@
         <v>46707.11132650308</v>
       </c>
       <c r="P94" t="n">
-        <v>45215.2177305423</v>
+        <v>45215.21773054231</v>
       </c>
       <c r="Q94" t="n">
         <v>38780.65333177381</v>
@@ -6474,7 +6474,7 @@
         <v>40379.02430056832</v>
       </c>
       <c r="T94" t="n">
-        <v>44952.95204661557</v>
+        <v>44952.95204661556</v>
       </c>
     </row>
     <row r="95">
@@ -6493,7 +6493,7 @@
         <v>52442.95831680649</v>
       </c>
       <c r="E95" t="n">
-        <v>58408.13050153569</v>
+        <v>58408.13050153568</v>
       </c>
       <c r="F95" t="n">
         <v>41114.51801673223</v>
@@ -6508,16 +6508,16 @@
         <v>55120.97638116551</v>
       </c>
       <c r="J95" t="n">
-        <v>48153.72944013632</v>
+        <v>48153.72944013631</v>
       </c>
       <c r="K95" t="n">
-        <v>50457.19211335544</v>
+        <v>50457.19211335545</v>
       </c>
       <c r="L95" t="n">
         <v>48460.06747734948</v>
       </c>
       <c r="M95" t="n">
-        <v>47287.65712769314</v>
+        <v>47287.65712769313</v>
       </c>
       <c r="N95" t="n">
         <v>49534.54990603718</v>
@@ -6526,7 +6526,7 @@
         <v>48479.83215935489</v>
       </c>
       <c r="P95" t="n">
-        <v>54640.21390571663</v>
+        <v>54640.21390571662</v>
       </c>
       <c r="Q95" t="n">
         <v>44388.52453644572</v>
@@ -6554,10 +6554,10 @@
         <v>11678.59900428366</v>
       </c>
       <c r="D96" t="n">
-        <v>9397.419788682344</v>
+        <v>9397.419788682342</v>
       </c>
       <c r="E96" t="n">
-        <v>9236.086944833625</v>
+        <v>9236.086944833623</v>
       </c>
       <c r="F96" t="n">
         <v>8825.520524171667</v>
@@ -6566,7 +6566,7 @@
         <v>9873.394193487155</v>
       </c>
       <c r="H96" t="n">
-        <v>14606.16515514862</v>
+        <v>14606.16515514863</v>
       </c>
       <c r="I96" t="n">
         <v>15775.83805770039</v>
@@ -6587,19 +6587,19 @@
         <v>16400.933893594</v>
       </c>
       <c r="O96" t="n">
-        <v>25096.70405426961</v>
+        <v>25096.7040542696</v>
       </c>
       <c r="P96" t="n">
         <v>22053.78766617034</v>
       </c>
       <c r="Q96" t="n">
-        <v>22287.63271624223</v>
+        <v>22287.63271624222</v>
       </c>
       <c r="R96" t="n">
         <v>26803.2804016814</v>
       </c>
       <c r="S96" t="n">
-        <v>27638.50626297128</v>
+        <v>27638.50626297129</v>
       </c>
       <c r="T96" t="n">
         <v>26527.48431366601</v>
@@ -6621,16 +6621,16 @@
         <v>4297.302297741757</v>
       </c>
       <c r="E97" t="n">
-        <v>3712.202346593021</v>
+        <v>3712.202346593022</v>
       </c>
       <c r="F97" t="n">
-        <v>3533.055802173124</v>
+        <v>3533.055802173123</v>
       </c>
       <c r="G97" t="n">
         <v>3784.792931948576</v>
       </c>
       <c r="H97" t="n">
-        <v>3553.46003913923</v>
+        <v>3553.460039139231</v>
       </c>
       <c r="I97" t="n">
         <v>5365.044426398484</v>
@@ -6648,7 +6648,7 @@
         <v>5665.861028585833</v>
       </c>
       <c r="N97" t="n">
-        <v>5788.768932954658</v>
+        <v>5788.768932954659</v>
       </c>
       <c r="O97" t="n">
         <v>8178.127707139322</v>
@@ -6682,7 +6682,7 @@
         <v>8143.325214967454</v>
       </c>
       <c r="D98" t="n">
-        <v>7770.782158689799</v>
+        <v>7770.7821586898</v>
       </c>
       <c r="E98" t="n">
         <v>7572.52316405507</v>
@@ -6691,19 +6691,19 @@
         <v>7236.04413386451</v>
       </c>
       <c r="G98" t="n">
-        <v>7062.471798943196</v>
+        <v>7062.471798943195</v>
       </c>
       <c r="H98" t="n">
-        <v>9189.945413996862</v>
+        <v>9189.94541399686</v>
       </c>
       <c r="I98" t="n">
         <v>10907.24551685863</v>
       </c>
       <c r="J98" t="n">
-        <v>8613.961155717456</v>
+        <v>8613.961155717458</v>
       </c>
       <c r="K98" t="n">
-        <v>9502.507816419877</v>
+        <v>9502.507816419875</v>
       </c>
       <c r="L98" t="n">
         <v>11149.38081806627</v>
@@ -6715,7 +6715,7 @@
         <v>10915.64130924323</v>
       </c>
       <c r="O98" t="n">
-        <v>16484.29233354786</v>
+        <v>16484.29233354785</v>
       </c>
       <c r="P98" t="n">
         <v>17656.9326326855</v>
@@ -6730,7 +6730,7 @@
         <v>17309.76146596188</v>
       </c>
       <c r="T98" t="n">
-        <v>18881.21820554011</v>
+        <v>18881.21820554012</v>
       </c>
     </row>
     <row r="99">
@@ -6743,16 +6743,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6786.271918448506</v>
+        <v>6786.271918448507</v>
       </c>
       <c r="D99" t="n">
-        <v>5720.384615362669</v>
+        <v>5720.38461536267</v>
       </c>
       <c r="E99" t="n">
-        <v>7174.283411490228</v>
+        <v>7174.283411490226</v>
       </c>
       <c r="F99" t="n">
-        <v>6613.949407483243</v>
+        <v>6613.949407483242</v>
       </c>
       <c r="G99" t="n">
         <v>7059.199259329073</v>
@@ -6810,16 +6810,16 @@
         <v>5569.664219325762</v>
       </c>
       <c r="D100" t="n">
-        <v>4877.786724590384</v>
+        <v>4877.786724590385</v>
       </c>
       <c r="E100" t="n">
-        <v>5457.283108875224</v>
+        <v>5457.283108875225</v>
       </c>
       <c r="F100" t="n">
         <v>4288.800998551603</v>
       </c>
       <c r="G100" t="n">
-        <v>4149.898169491373</v>
+        <v>4149.898169491374</v>
       </c>
       <c r="H100" t="n">
         <v>5301.436942434799</v>
@@ -6831,13 +6831,13 @@
         <v>5333.477182742661</v>
       </c>
       <c r="K100" t="n">
-        <v>5272.579362809154</v>
+        <v>5272.579362809153</v>
       </c>
       <c r="L100" t="n">
         <v>5770.333867896004</v>
       </c>
       <c r="M100" t="n">
-        <v>5606.58151580593</v>
+        <v>5606.581515805929</v>
       </c>
       <c r="N100" t="n">
         <v>5930.567660132197</v>
@@ -6858,7 +6858,7 @@
         <v>8328.920929837268</v>
       </c>
       <c r="T100" t="n">
-        <v>9260.467387176279</v>
+        <v>9260.467387176281</v>
       </c>
     </row>
     <row r="101">
@@ -6913,7 +6913,7 @@
         <v>22319.8218224391</v>
       </c>
       <c r="Q101" t="n">
-        <v>21489.1756011784</v>
+        <v>21489.17560117839</v>
       </c>
       <c r="R101" t="n">
         <v>24598.74440890038</v>
@@ -6944,10 +6944,10 @@
         <v>122089.5332756666</v>
       </c>
       <c r="F102" t="n">
-        <v>93695.78788320186</v>
+        <v>93695.78788320188</v>
       </c>
       <c r="G102" t="n">
-        <v>97762.52069046324</v>
+        <v>97762.52069046322</v>
       </c>
       <c r="H102" t="n">
         <v>128014.3653857233</v>
@@ -7005,7 +7005,7 @@
         <v>1685.135552937777</v>
       </c>
       <c r="E103" t="n">
-        <v>1662.04579760401</v>
+        <v>1662.045797604009</v>
       </c>
       <c r="F103" t="n">
         <v>1518.391331384132</v>
@@ -7066,10 +7066,10 @@
         <v>6931.176816185596</v>
       </c>
       <c r="D104" t="n">
-        <v>6654.424747760474</v>
+        <v>6654.424747760473</v>
       </c>
       <c r="E104" t="n">
-        <v>6375.768564586226</v>
+        <v>6375.768564586225</v>
       </c>
       <c r="F104" t="n">
         <v>5788.365015934566</v>
@@ -7078,10 +7078,10 @@
         <v>6013.010073799001</v>
       </c>
       <c r="H104" t="n">
-        <v>4901.180901021341</v>
+        <v>4901.180901021342</v>
       </c>
       <c r="I104" t="n">
-        <v>7532.164075237849</v>
+        <v>7532.164075237848</v>
       </c>
       <c r="J104" t="n">
         <v>6351.209601041864</v>
@@ -7090,16 +7090,16 @@
         <v>6767.24729103661</v>
       </c>
       <c r="L104" t="n">
-        <v>7125.503731189931</v>
+        <v>7125.50373118993</v>
       </c>
       <c r="M104" t="n">
         <v>6829.507015028908</v>
       </c>
       <c r="N104" t="n">
-        <v>7488.336677330549</v>
+        <v>7488.336677330548</v>
       </c>
       <c r="O104" t="n">
-        <v>9093.91221507095</v>
+        <v>9093.912215070952</v>
       </c>
       <c r="P104" t="n">
         <v>9062.76181470685</v>
@@ -7108,10 +7108,10 @@
         <v>8471.372209357389</v>
       </c>
       <c r="R104" t="n">
-        <v>8996.415658431479</v>
+        <v>8996.415658431477</v>
       </c>
       <c r="S104" t="n">
-        <v>8886.442821751209</v>
+        <v>8886.44282175121</v>
       </c>
       <c r="T104" t="n">
         <v>10229.20883010626</v>
@@ -7145,7 +7145,7 @@
         <v>6345.793881603221</v>
       </c>
       <c r="I105" t="n">
-        <v>9603.517646482826</v>
+        <v>9603.517646482827</v>
       </c>
       <c r="J105" t="n">
         <v>8441.840918544793</v>
@@ -7258,10 +7258,10 @@
         <v>11290.84936253866</v>
       </c>
       <c r="D107" t="n">
-        <v>9295.563609675562</v>
+        <v>9295.563609675564</v>
       </c>
       <c r="E107" t="n">
-        <v>7051.587584669223</v>
+        <v>7051.587584669222</v>
       </c>
       <c r="F107" t="n">
         <v>9074.314118770691</v>
@@ -7282,7 +7282,7 @@
         <v>11372.3742134611</v>
       </c>
       <c r="L107" t="n">
-        <v>9741.565507383131</v>
+        <v>9741.565507383129</v>
       </c>
       <c r="M107" t="n">
         <v>11107.23107039248</v>
@@ -7322,40 +7322,40 @@
         <v>46988.87067649853</v>
       </c>
       <c r="D108" t="n">
-        <v>42587.69104887746</v>
+        <v>42587.69104887745</v>
       </c>
       <c r="E108" t="n">
-        <v>43293.40139103819</v>
+        <v>43293.40139103818</v>
       </c>
       <c r="F108" t="n">
         <v>38496.77015692973</v>
       </c>
       <c r="G108" t="n">
-        <v>39975.4795082687</v>
+        <v>39975.47950826868</v>
       </c>
       <c r="H108" t="n">
-        <v>47808.93725117197</v>
+        <v>47808.93725117198</v>
       </c>
       <c r="I108" t="n">
-        <v>57562.81848226741</v>
+        <v>57562.81848226742</v>
       </c>
       <c r="J108" t="n">
         <v>50485.5626048266</v>
       </c>
       <c r="K108" t="n">
-        <v>50258.1063603358</v>
+        <v>50258.10636033579</v>
       </c>
       <c r="L108" t="n">
-        <v>51946.24353501144</v>
+        <v>51946.24353501142</v>
       </c>
       <c r="M108" t="n">
         <v>51735.32828009796</v>
       </c>
       <c r="N108" t="n">
-        <v>54765.78671270717</v>
+        <v>54765.78671270715</v>
       </c>
       <c r="O108" t="n">
-        <v>71140.37802761963</v>
+        <v>71140.37802761962</v>
       </c>
       <c r="P108" t="n">
         <v>77236.85304101232</v>
@@ -7364,13 +7364,13 @@
         <v>67874.67335722284</v>
       </c>
       <c r="R108" t="n">
-        <v>80646.93920226865</v>
+        <v>80646.93920226861</v>
       </c>
       <c r="S108" t="n">
-        <v>71661.81449635695</v>
+        <v>71661.81449635699</v>
       </c>
       <c r="T108" t="n">
-        <v>82942.64916214727</v>
+        <v>82942.64916214725</v>
       </c>
     </row>
     <row r="109">
@@ -7428,13 +7428,13 @@
         <v>392.735682109298</v>
       </c>
       <c r="R109" t="n">
-        <v>415.6869362752921</v>
+        <v>415.686936275292</v>
       </c>
       <c r="S109" t="n">
         <v>442.80648140421</v>
       </c>
       <c r="T109" t="n">
-        <v>387.6761475700279</v>
+        <v>387.6761475700278</v>
       </c>
     </row>
     <row r="110">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9741.694922835328</v>
+        <v>9741.694922835326</v>
       </c>
       <c r="D110" t="n">
         <v>8915.109343647477</v>
       </c>
       <c r="E110" t="n">
-        <v>7427.793441556443</v>
+        <v>7427.793441556444</v>
       </c>
       <c r="F110" t="n">
         <v>7118.350834382766</v>
@@ -7471,13 +7471,13 @@
         <v>9448.976229145024</v>
       </c>
       <c r="K110" t="n">
-        <v>10437.36761287137</v>
+        <v>10437.36761287136</v>
       </c>
       <c r="L110" t="n">
         <v>11059.43607883944</v>
       </c>
       <c r="M110" t="n">
-        <v>10472.2328184997</v>
+        <v>10472.23281849969</v>
       </c>
       <c r="N110" t="n">
         <v>10544.95766535858</v>
@@ -7489,7 +7489,7 @@
         <v>16853.63127609419</v>
       </c>
       <c r="Q110" t="n">
-        <v>9886.196187398236</v>
+        <v>9886.196187398235</v>
       </c>
       <c r="R110" t="n">
         <v>17291.39079886286</v>
@@ -7514,7 +7514,7 @@
         <v>228603.752525775</v>
       </c>
       <c r="D111" t="n">
-        <v>207930.1467297032</v>
+        <v>207930.1467297031</v>
       </c>
       <c r="E111" t="n">
         <v>219556.3245887887</v>
@@ -7529,13 +7529,13 @@
         <v>230494.7790033868</v>
       </c>
       <c r="I111" t="n">
-        <v>244475.400031209</v>
+        <v>244475.4000312089</v>
       </c>
       <c r="J111" t="n">
         <v>203178.5579771679</v>
       </c>
       <c r="K111" t="n">
-        <v>212898.0985435025</v>
+        <v>212898.0985435024</v>
       </c>
       <c r="L111" t="n">
         <v>216929.4404875897</v>
@@ -7553,13 +7553,13 @@
         <v>276143.6979654676</v>
       </c>
       <c r="Q111" t="n">
-        <v>266768.2322749544</v>
+        <v>266768.2322749543</v>
       </c>
       <c r="R111" t="n">
         <v>290165.5454776472</v>
       </c>
       <c r="S111" t="n">
-        <v>316498.5708435581</v>
+        <v>316498.570843558</v>
       </c>
       <c r="T111" t="n">
         <v>315804.4808025059</v>
@@ -7581,7 +7581,7 @@
         <v>11331.04128536078</v>
       </c>
       <c r="E112" t="n">
-        <v>14301.62282648061</v>
+        <v>14301.6228264806</v>
       </c>
       <c r="F112" t="n">
         <v>10261.31591202302</v>
@@ -7596,7 +7596,7 @@
         <v>13602.0828247945</v>
       </c>
       <c r="J112" t="n">
-        <v>13124.43926334313</v>
+        <v>13124.43926334314</v>
       </c>
       <c r="K112" t="n">
         <v>12275.27161516756</v>
@@ -7617,7 +7617,7 @@
         <v>16879.33593510006</v>
       </c>
       <c r="Q112" t="n">
-        <v>18867.44346175299</v>
+        <v>18867.44346175298</v>
       </c>
       <c r="R112" t="n">
         <v>18859.76413557756</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5442.482161707709</v>
+        <v>5442.48216170771</v>
       </c>
       <c r="D113" t="n">
         <v>3522.418911119416</v>
@@ -7648,13 +7648,13 @@
         <v>3765.42044767097</v>
       </c>
       <c r="F113" t="n">
-        <v>2934.109123532495</v>
+        <v>2934.109123532494</v>
       </c>
       <c r="G113" t="n">
         <v>2980.309914421961</v>
       </c>
       <c r="H113" t="n">
-        <v>5604.976106893272</v>
+        <v>5604.976106893271</v>
       </c>
       <c r="I113" t="n">
         <v>4988.085535794981</v>
@@ -7675,7 +7675,7 @@
         <v>4994.028921577184</v>
       </c>
       <c r="O113" t="n">
-        <v>6518.727172082447</v>
+        <v>6518.727172082446</v>
       </c>
       <c r="P113" t="n">
         <v>7176.277928076621</v>
@@ -7690,7 +7690,7 @@
         <v>9504.877005582424</v>
       </c>
       <c r="T113" t="n">
-        <v>8248.981067599469</v>
+        <v>8248.98106759947</v>
       </c>
     </row>
     <row r="114">
@@ -7709,7 +7709,7 @@
         <v>990.5924277224822</v>
       </c>
       <c r="E114" t="n">
-        <v>769.0705577518966</v>
+        <v>769.0705577518967</v>
       </c>
       <c r="F114" t="n">
         <v>837.0874594811785</v>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5240.067115097502</v>
+        <v>5240.067115097503</v>
       </c>
       <c r="D116" t="n">
         <v>4760.655580977366</v>
@@ -7846,13 +7846,13 @@
         <v>4271.28582183668</v>
       </c>
       <c r="H116" t="n">
-        <v>4344.188015074927</v>
+        <v>4344.188015074928</v>
       </c>
       <c r="I116" t="n">
         <v>5393.844596951802</v>
       </c>
       <c r="J116" t="n">
-        <v>4476.335192708612</v>
+        <v>4476.335192708613</v>
       </c>
       <c r="K116" t="n">
         <v>4804.854896851054</v>
@@ -7873,16 +7873,16 @@
         <v>6183.971511760446</v>
       </c>
       <c r="Q116" t="n">
-        <v>6016.991430275694</v>
+        <v>6016.991430275693</v>
       </c>
       <c r="R116" t="n">
-        <v>6120.881875203119</v>
+        <v>6120.88187520312</v>
       </c>
       <c r="S116" t="n">
-        <v>6270.103573418801</v>
+        <v>6270.1035734188</v>
       </c>
       <c r="T116" t="n">
-        <v>7141.623523276753</v>
+        <v>7141.623523276752</v>
       </c>
     </row>
     <row r="117">
@@ -7913,7 +7913,7 @@
         <v>4640.755591094019</v>
       </c>
       <c r="I117" t="n">
-        <v>7577.261983988716</v>
+        <v>7577.261983988715</v>
       </c>
       <c r="J117" t="n">
         <v>5595.406100441343</v>
@@ -7922,7 +7922,7 @@
         <v>6561.812202582941</v>
       </c>
       <c r="L117" t="n">
-        <v>6614.718152045566</v>
+        <v>6614.718152045565</v>
       </c>
       <c r="M117" t="n">
         <v>6241.994802619824</v>
@@ -7943,7 +7943,7 @@
         <v>13255.06087262872</v>
       </c>
       <c r="S117" t="n">
-        <v>16023.4764604963</v>
+        <v>16023.47646049629</v>
       </c>
       <c r="T117" t="n">
         <v>17266.36266116699</v>
@@ -7977,7 +7977,7 @@
         <v>281.7601803222536</v>
       </c>
       <c r="I118" t="n">
-        <v>462.8902937883113</v>
+        <v>462.8902937883114</v>
       </c>
       <c r="J118" t="n">
         <v>416.7456900212628</v>
@@ -7998,13 +7998,13 @@
         <v>573.5635946884249</v>
       </c>
       <c r="P118" t="n">
-        <v>685.8309130896035</v>
+        <v>685.8309130896037</v>
       </c>
       <c r="Q118" t="n">
-        <v>660.5944378125201</v>
+        <v>660.5944378125203</v>
       </c>
       <c r="R118" t="n">
-        <v>830.1529448864125</v>
+        <v>830.1529448864126</v>
       </c>
       <c r="S118" t="n">
         <v>800.88809267027</v>
@@ -8029,7 +8029,7 @@
         <v>24077.59006447189</v>
       </c>
       <c r="E119" t="n">
-        <v>26615.58935015002</v>
+        <v>26615.58935015001</v>
       </c>
       <c r="F119" t="n">
         <v>28043.38654488868</v>
@@ -8041,16 +8041,16 @@
         <v>28187.41081066774</v>
       </c>
       <c r="I119" t="n">
-        <v>47554.23841579899</v>
+        <v>47554.23841579897</v>
       </c>
       <c r="J119" t="n">
-        <v>40682.84025833802</v>
+        <v>40682.84025833801</v>
       </c>
       <c r="K119" t="n">
         <v>42739.68416186672</v>
       </c>
       <c r="L119" t="n">
-        <v>47277.69908570982</v>
+        <v>47277.69908570983</v>
       </c>
       <c r="M119" t="n">
         <v>43306.34879049732</v>
@@ -8059,7 +8059,7 @@
         <v>47812.99286286454</v>
       </c>
       <c r="O119" t="n">
-        <v>60217.31688497404</v>
+        <v>60217.31688497403</v>
       </c>
       <c r="P119" t="n">
         <v>63828.03113423785</v>
@@ -8068,13 +8068,13 @@
         <v>54838.09693599131</v>
       </c>
       <c r="R119" t="n">
-        <v>65158.4324781598</v>
+        <v>65158.43247815978</v>
       </c>
       <c r="S119" t="n">
         <v>65024.10007347762</v>
       </c>
       <c r="T119" t="n">
-        <v>66541.84374152457</v>
+        <v>66541.84374152459</v>
       </c>
     </row>
     <row r="120">
@@ -8096,34 +8096,34 @@
         <v>5228544.5905904</v>
       </c>
       <c r="F120" t="n">
-        <v>4495164.84161878</v>
+        <v>4495164.841618779</v>
       </c>
       <c r="G120" t="n">
-        <v>4561652.818100051</v>
+        <v>4561652.81810005</v>
       </c>
       <c r="H120" t="n">
-        <v>6500764.046336509</v>
+        <v>6500764.046336506</v>
       </c>
       <c r="I120" t="n">
-        <v>7490945.778593908</v>
+        <v>7490945.778593906</v>
       </c>
       <c r="J120" t="n">
-        <v>6302272.447076579</v>
+        <v>6302272.447076576</v>
       </c>
       <c r="K120" t="n">
-        <v>6221798.180198313</v>
+        <v>6221798.180198312</v>
       </c>
       <c r="L120" t="n">
         <v>8407287.033376593</v>
       </c>
       <c r="M120" t="n">
-        <v>8111690.01639209</v>
+        <v>8111690.016392088</v>
       </c>
       <c r="N120" t="n">
-        <v>7491772.461627171</v>
+        <v>7491772.461627173</v>
       </c>
       <c r="O120" t="n">
-        <v>17195689.66156703</v>
+        <v>17195689.66156704</v>
       </c>
       <c r="P120" t="n">
         <v>16966631.89089487</v>
@@ -8254,7 +8254,7 @@
         <v>2878.397139913887</v>
       </c>
       <c r="P122" t="n">
-        <v>3097.538166620541</v>
+        <v>3097.538166620542</v>
       </c>
       <c r="Q122" t="n">
         <v>2173.05826891201</v>
@@ -8266,7 +8266,7 @@
         <v>2277.258182589449</v>
       </c>
       <c r="T122" t="n">
-        <v>2837.692346924847</v>
+        <v>2837.692346924846</v>
       </c>
     </row>
     <row r="123">
@@ -8279,31 +8279,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>46269.6192592183</v>
+        <v>46269.61925921829</v>
       </c>
       <c r="D123" t="n">
-        <v>43060.99024822606</v>
+        <v>43060.99024822605</v>
       </c>
       <c r="E123" t="n">
         <v>44151.44601895721</v>
       </c>
       <c r="F123" t="n">
-        <v>33855.16674163229</v>
+        <v>33855.16674163227</v>
       </c>
       <c r="G123" t="n">
-        <v>34951.39588507865</v>
+        <v>34951.39588507864</v>
       </c>
       <c r="H123" t="n">
         <v>40627.85247748348</v>
       </c>
       <c r="I123" t="n">
-        <v>52219.69577072909</v>
+        <v>52219.69577072908</v>
       </c>
       <c r="J123" t="n">
         <v>46336.578506944</v>
       </c>
       <c r="K123" t="n">
-        <v>46330.30402154793</v>
+        <v>46330.30402154791</v>
       </c>
       <c r="L123" t="n">
         <v>50657.8406326388</v>
@@ -8312,25 +8312,25 @@
         <v>45500.59828224988</v>
       </c>
       <c r="N123" t="n">
-        <v>49921.89635763374</v>
+        <v>49921.89635763375</v>
       </c>
       <c r="O123" t="n">
         <v>70999.16900957277</v>
       </c>
       <c r="P123" t="n">
-        <v>73583.06820675143</v>
+        <v>73583.06820675141</v>
       </c>
       <c r="Q123" t="n">
-        <v>81216.53097633901</v>
+        <v>81216.53097633903</v>
       </c>
       <c r="R123" t="n">
-        <v>87065.32829119754</v>
+        <v>87065.32829119753</v>
       </c>
       <c r="S123" t="n">
         <v>104216.0573211567</v>
       </c>
       <c r="T123" t="n">
-        <v>95045.92824886237</v>
+        <v>95045.92824886236</v>
       </c>
     </row>
     <row r="124">
@@ -8358,7 +8358,7 @@
         <v>48448.41710360779</v>
       </c>
       <c r="H124" t="n">
-        <v>43419.04617597859</v>
+        <v>43419.04617597858</v>
       </c>
       <c r="I124" t="n">
         <v>56213.86204447289</v>
@@ -8379,16 +8379,16 @@
         <v>56924.85597220746</v>
       </c>
       <c r="O124" t="n">
-        <v>72345.52951428269</v>
+        <v>72345.52951428268</v>
       </c>
       <c r="P124" t="n">
         <v>77585.43893186044</v>
       </c>
       <c r="Q124" t="n">
-        <v>59890.88550747322</v>
+        <v>59890.88550747323</v>
       </c>
       <c r="R124" t="n">
-        <v>73291.23334956836</v>
+        <v>73291.23334956834</v>
       </c>
       <c r="S124" t="n">
         <v>71729.79171310509</v>
@@ -8443,7 +8443,7 @@
         <v>233172.4111305304</v>
       </c>
       <c r="O125" t="n">
-        <v>276942.3444859537</v>
+        <v>276942.3444859538</v>
       </c>
       <c r="P125" t="n">
         <v>286599.7296186012</v>
@@ -8452,13 +8452,13 @@
         <v>278101.094211526</v>
       </c>
       <c r="R125" t="n">
-        <v>278237.1158883548</v>
+        <v>278237.1158883547</v>
       </c>
       <c r="S125" t="n">
-        <v>293182.6961506414</v>
+        <v>293182.6961506413</v>
       </c>
       <c r="T125" t="n">
-        <v>362653.9470449959</v>
+        <v>362653.9470449958</v>
       </c>
     </row>
     <row r="126">
@@ -8562,10 +8562,10 @@
         <v>29255.5122484863</v>
       </c>
       <c r="L127" t="n">
-        <v>35365.42791773861</v>
+        <v>35365.42791773862</v>
       </c>
       <c r="M127" t="n">
-        <v>31567.67815178209</v>
+        <v>31567.67815178208</v>
       </c>
       <c r="N127" t="n">
         <v>32677.52297835895</v>
@@ -8580,7 +8580,7 @@
         <v>63755.71240949781</v>
       </c>
       <c r="R127" t="n">
-        <v>69551.41727955744</v>
+        <v>69551.41727955746</v>
       </c>
       <c r="S127" t="n">
         <v>75972.3815794806</v>
@@ -8745,7 +8745,7 @@
         <v>2841.497274353714</v>
       </c>
       <c r="I130" t="n">
-        <v>4441.45754169148</v>
+        <v>4441.457541691479</v>
       </c>
       <c r="J130" t="n">
         <v>3829.642286321425</v>
@@ -8760,25 +8760,25 @@
         <v>3838.833671151439</v>
       </c>
       <c r="N130" t="n">
-        <v>4056.839034766303</v>
+        <v>4056.839034766302</v>
       </c>
       <c r="O130" t="n">
         <v>6750.004444686045</v>
       </c>
       <c r="P130" t="n">
-        <v>6790.932545599001</v>
+        <v>6790.932545599002</v>
       </c>
       <c r="Q130" t="n">
-        <v>5845.334169897374</v>
+        <v>5845.334169897375</v>
       </c>
       <c r="R130" t="n">
-        <v>7354.577198524458</v>
+        <v>7354.577198524457</v>
       </c>
       <c r="S130" t="n">
-        <v>6860.605909277372</v>
+        <v>6860.605909277373</v>
       </c>
       <c r="T130" t="n">
-        <v>7766.238154946131</v>
+        <v>7766.23815494613</v>
       </c>
     </row>
     <row r="131">
@@ -8800,7 +8800,7 @@
         <v>10671.08495405078</v>
       </c>
       <c r="F131" t="n">
-        <v>9573.487946815056</v>
+        <v>9573.487946815058</v>
       </c>
       <c r="G131" t="n">
         <v>10219.90222323136</v>
@@ -8821,7 +8821,7 @@
         <v>14053.49705574795</v>
       </c>
       <c r="M131" t="n">
-        <v>13664.36835970684</v>
+        <v>13664.36835970683</v>
       </c>
       <c r="N131" t="n">
         <v>14495.39291747512</v>
@@ -8830,7 +8830,7 @@
         <v>19333.30718984256</v>
       </c>
       <c r="P131" t="n">
-        <v>19459.7819082927</v>
+        <v>19459.78190829271</v>
       </c>
       <c r="Q131" t="n">
         <v>19176.03054415409</v>
@@ -8861,28 +8861,28 @@
         <v>6206.329712218401</v>
       </c>
       <c r="E132" t="n">
-        <v>5852.949994570459</v>
+        <v>5852.949994570458</v>
       </c>
       <c r="F132" t="n">
-        <v>5533.412026396724</v>
+        <v>5533.412026396725</v>
       </c>
       <c r="G132" t="n">
-        <v>5676.871927857166</v>
+        <v>5676.871927857165</v>
       </c>
       <c r="H132" t="n">
         <v>7838.684549875953</v>
       </c>
       <c r="I132" t="n">
-        <v>9330.508671050435</v>
+        <v>9330.508671050437</v>
       </c>
       <c r="J132" t="n">
         <v>7475.637600659608</v>
       </c>
       <c r="K132" t="n">
-        <v>7892.242827091175</v>
+        <v>7892.242827091174</v>
       </c>
       <c r="L132" t="n">
-        <v>8159.17587558603</v>
+        <v>8159.175875586031</v>
       </c>
       <c r="M132" t="n">
         <v>7641.745101812402</v>
@@ -8943,7 +8943,7 @@
         <v>68186.68081629918</v>
       </c>
       <c r="K133" t="n">
-        <v>65666.60822821154</v>
+        <v>65666.60822821155</v>
       </c>
       <c r="L133" t="n">
         <v>79828.81918274953</v>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>280.9467671737408</v>
+        <v>280.9467671737409</v>
       </c>
       <c r="D134" t="n">
         <v>228.2224434285224</v>
@@ -9022,7 +9022,7 @@
         <v>221.327065634928</v>
       </c>
       <c r="P134" t="n">
-        <v>317.309195723872</v>
+        <v>317.3091957238721</v>
       </c>
       <c r="Q134" t="n">
         <v>226.9408919718908</v>
@@ -9092,13 +9092,13 @@
         <v>4389.379091406804</v>
       </c>
       <c r="R135" t="n">
-        <v>4663.225446449592</v>
+        <v>4663.225446449593</v>
       </c>
       <c r="S135" t="n">
         <v>4972.912637157366</v>
       </c>
       <c r="T135" t="n">
-        <v>5514.636117874775</v>
+        <v>5514.636117874776</v>
       </c>
     </row>
     <row r="136">
@@ -9190,7 +9190,7 @@
         <v>2437.913129612393</v>
       </c>
       <c r="H137" t="n">
-        <v>2375.759871411725</v>
+        <v>2375.759871411724</v>
       </c>
       <c r="I137" t="n">
         <v>2891.257756414504</v>
@@ -9202,10 +9202,10 @@
         <v>2832.024724373194</v>
       </c>
       <c r="L137" t="n">
-        <v>3208.029839892779</v>
+        <v>3208.029839892778</v>
       </c>
       <c r="M137" t="n">
-        <v>3286.385732447424</v>
+        <v>3286.385732447425</v>
       </c>
       <c r="N137" t="n">
         <v>3135.963916429927</v>
@@ -9245,7 +9245,7 @@
         <v>1316.865875041022</v>
       </c>
       <c r="E138" t="n">
-        <v>588.918437379624</v>
+        <v>588.9184373796239</v>
       </c>
       <c r="F138" t="n">
         <v>1145.263859946307</v>
@@ -9269,7 +9269,7 @@
         <v>1563.424171897504</v>
       </c>
       <c r="M138" t="n">
-        <v>659.3700869441291</v>
+        <v>659.370086944129</v>
       </c>
       <c r="N138" t="n">
         <v>1528.034800715324</v>
@@ -9281,7 +9281,7 @@
         <v>903.4244905161411</v>
       </c>
       <c r="Q138" t="n">
-        <v>2484.720872050091</v>
+        <v>2484.720872050092</v>
       </c>
       <c r="R138" t="n">
         <v>881.0423729083834</v>
@@ -9309,7 +9309,7 @@
         <v>1554.756290603921</v>
       </c>
       <c r="E139" t="n">
-        <v>823.0760183658365</v>
+        <v>823.0760183658364</v>
       </c>
       <c r="F139" t="n">
         <v>1344.964904394327</v>
@@ -9330,7 +9330,7 @@
         <v>1760.773242298024</v>
       </c>
       <c r="L139" t="n">
-        <v>1854.809249500245</v>
+        <v>1854.809249500244</v>
       </c>
       <c r="M139" t="n">
         <v>991.5123076256882</v>
@@ -9339,7 +9339,7 @@
         <v>1888.863592881923</v>
       </c>
       <c r="O139" t="n">
-        <v>2854.504128655315</v>
+        <v>2854.504128655316</v>
       </c>
       <c r="P139" t="n">
         <v>1483.224167083734</v>
